--- a/data/itemliste_v7.xlsx
+++ b/data/itemliste_v7.xlsx
@@ -31559,7 +31559,7 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R3" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R4" t="inlineStr">
         <is>
@@ -31751,7 +31751,7 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R5" t="inlineStr">
         <is>
@@ -31839,7 +31839,7 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R6" t="inlineStr">
         <is>
@@ -31935,7 +31935,7 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P7" t="inlineStr">
         <is>
@@ -31943,7 +31943,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R7" t="inlineStr">
         <is>
@@ -32031,7 +32031,7 @@
         <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P8" t="inlineStr">
         <is>
@@ -32039,7 +32039,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -32127,7 +32127,7 @@
         <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P9" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R9" t="inlineStr">
         <is>
@@ -32150,6 +32150,11 @@
       <c r="T9" t="inlineStr">
         <is>
           <t>Schildbuckel</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V9" t="n">
@@ -32256,7 +32261,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R11" t="inlineStr">
         <is>
@@ -32352,7 +32357,7 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R12" t="inlineStr">
         <is>
@@ -32448,7 +32453,7 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R13" t="inlineStr">
         <is>
@@ -32536,7 +32541,7 @@
         <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
@@ -32544,7 +32549,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R14" t="inlineStr">
         <is>
@@ -32632,7 +32637,7 @@
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
@@ -32640,7 +32645,7 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R15" t="inlineStr">
         <is>
@@ -32728,7 +32733,7 @@
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
@@ -32736,7 +32741,7 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R16" t="inlineStr">
         <is>
@@ -32824,7 +32829,7 @@
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
@@ -32832,7 +32837,7 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R17" t="inlineStr">
         <is>
@@ -32847,6 +32852,11 @@
       <c r="T17" t="inlineStr">
         <is>
           <t>Großschild + Stützarm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V17" t="n">
@@ -32953,7 +32963,7 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R19" t="inlineStr">
         <is>
@@ -33049,7 +33059,7 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -33145,7 +33155,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R21" t="inlineStr">
         <is>
@@ -33233,7 +33243,7 @@
         <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" t="inlineStr">
         <is>
@@ -33241,7 +33251,7 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R22" t="inlineStr">
         <is>
@@ -33329,7 +33339,7 @@
         <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P23" t="inlineStr">
         <is>
@@ -33337,7 +33347,7 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R23" t="inlineStr">
         <is>
@@ -33425,7 +33435,7 @@
         <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P24" t="inlineStr">
         <is>
@@ -33433,7 +33443,7 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R24" t="inlineStr">
         <is>
@@ -33521,7 +33531,7 @@
         <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P25" t="inlineStr">
         <is>
@@ -33529,7 +33539,7 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R25" t="inlineStr">
         <is>
@@ -33544,6 +33554,11 @@
       <c r="T25" t="inlineStr">
         <is>
           <t>Einband + Seiten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V25" t="n">
@@ -33650,7 +33665,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R27" t="inlineStr">
         <is>
@@ -33746,7 +33761,7 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R28" t="inlineStr">
         <is>
@@ -33842,7 +33857,7 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R29" t="inlineStr">
         <is>
@@ -33930,7 +33945,7 @@
         <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P30" t="inlineStr">
         <is>
@@ -33938,7 +33953,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R30" t="inlineStr">
         <is>
@@ -34026,7 +34041,7 @@
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -34034,7 +34049,7 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R31" t="inlineStr">
         <is>
@@ -34122,7 +34137,7 @@
         <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
@@ -34130,7 +34145,7 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R32" t="inlineStr">
         <is>
@@ -34218,7 +34233,7 @@
         <v>7</v>
       </c>
       <c r="O33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P33" t="inlineStr">
         <is>
@@ -34226,7 +34241,7 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R33" t="inlineStr">
         <is>
@@ -34241,6 +34256,11 @@
       <c r="T33" t="inlineStr">
         <is>
           <t>Geschliffener Kristall</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V33" t="n">
@@ -34347,7 +34367,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R35" t="inlineStr">
         <is>
@@ -34443,7 +34463,7 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R36" t="inlineStr">
         <is>
@@ -34539,7 +34559,7 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R37" t="inlineStr">
         <is>
@@ -34627,7 +34647,7 @@
         <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
@@ -34635,7 +34655,7 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R38" t="inlineStr">
         <is>
@@ -34723,7 +34743,7 @@
         <v>5</v>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -34731,7 +34751,7 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R39" t="inlineStr">
         <is>
@@ -34819,7 +34839,7 @@
         <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -34827,7 +34847,7 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R40" t="inlineStr">
         <is>
@@ -34915,7 +34935,7 @@
         <v>7</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -34923,7 +34943,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R41" t="inlineStr">
         <is>
@@ -34938,6 +34958,11 @@
       <c r="T41" t="inlineStr">
         <is>
           <t>Kette + Griffring</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V41" t="n">
@@ -35044,7 +35069,7 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R43" t="inlineStr">
         <is>
@@ -35140,7 +35165,7 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R44" t="inlineStr">
         <is>
@@ -35236,7 +35261,7 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R45" t="inlineStr">
         <is>
@@ -35324,7 +35349,7 @@
         <v>4</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -35332,7 +35357,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R46" t="inlineStr">
         <is>
@@ -35420,7 +35445,7 @@
         <v>5</v>
       </c>
       <c r="O47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -35428,7 +35453,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R47" t="inlineStr">
         <is>
@@ -35516,7 +35541,7 @@
         <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -35524,7 +35549,7 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R48" t="inlineStr">
         <is>
@@ -35612,7 +35637,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -35620,7 +35645,7 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R49" t="inlineStr">
         <is>
@@ -35635,6 +35660,11 @@
       <c r="T49" t="inlineStr">
         <is>
           <t>Gehäuse + Glas</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V49" t="n">
@@ -35741,7 +35771,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R51" t="inlineStr">
         <is>
@@ -35837,7 +35867,7 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R52" t="inlineStr">
         <is>
@@ -35933,7 +35963,7 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R53" t="inlineStr">
         <is>
@@ -36021,7 +36051,7 @@
         <v>4</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -36029,7 +36059,7 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R54" t="inlineStr">
         <is>
@@ -36117,7 +36147,7 @@
         <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -36125,7 +36155,7 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R55" t="inlineStr">
         <is>
@@ -36213,7 +36243,7 @@
         <v>6</v>
       </c>
       <c r="O56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -36221,7 +36251,7 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R56" t="inlineStr">
         <is>
@@ -36309,7 +36339,7 @@
         <v>7</v>
       </c>
       <c r="O57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
@@ -36317,7 +36347,7 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R57" t="inlineStr">
         <is>
@@ -36332,6 +36362,11 @@
       <c r="T57" t="inlineStr">
         <is>
           <t>Gurt + Schnalle</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V57" t="n">
@@ -36438,7 +36473,7 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R59" t="inlineStr">
         <is>
@@ -36534,7 +36569,7 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R60" t="inlineStr">
         <is>
@@ -36630,7 +36665,7 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R61" t="inlineStr">
         <is>
@@ -36718,7 +36753,7 @@
         <v>4</v>
       </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -36726,7 +36761,7 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R62" t="inlineStr">
         <is>
@@ -36814,7 +36849,7 @@
         <v>5</v>
       </c>
       <c r="O63" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -36822,7 +36857,7 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R63" t="inlineStr">
         <is>
@@ -36910,7 +36945,7 @@
         <v>6</v>
       </c>
       <c r="O64" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -36918,7 +36953,7 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R64" t="inlineStr">
         <is>
@@ -37006,7 +37041,7 @@
         <v>7</v>
       </c>
       <c r="O65" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -37014,7 +37049,7 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R65" t="inlineStr">
         <is>
@@ -37029,6 +37064,11 @@
       <c r="T65" t="inlineStr">
         <is>
           <t>Schaft + Pechkopf</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V65" t="n">
@@ -37135,7 +37175,7 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R67" t="inlineStr">
         <is>
@@ -37231,7 +37271,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R68" t="inlineStr">
         <is>
@@ -37327,7 +37367,7 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R69" t="inlineStr">
         <is>
@@ -37415,7 +37455,7 @@
         <v>4</v>
       </c>
       <c r="O70" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -37423,7 +37463,7 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R70" t="inlineStr">
         <is>
@@ -37511,7 +37551,7 @@
         <v>5</v>
       </c>
       <c r="O71" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -37519,7 +37559,7 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R71" t="inlineStr">
         <is>
@@ -37607,7 +37647,7 @@
         <v>6</v>
       </c>
       <c r="O72" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
@@ -37615,7 +37655,7 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R72" t="inlineStr">
         <is>
@@ -37703,7 +37743,7 @@
         <v>7</v>
       </c>
       <c r="O73" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
@@ -37711,7 +37751,7 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R73" t="inlineStr">
         <is>
@@ -37726,6 +37766,11 @@
       <c r="T73" t="inlineStr">
         <is>
           <t>Horn + Mundstück</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V73" t="n">
@@ -37832,7 +37877,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R75" t="inlineStr">
         <is>
@@ -37928,7 +37973,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R76" t="inlineStr">
         <is>
@@ -38024,7 +38069,7 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -38112,7 +38157,7 @@
         <v>4</v>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
@@ -38120,7 +38165,7 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R78" t="inlineStr">
         <is>
@@ -38208,7 +38253,7 @@
         <v>5</v>
       </c>
       <c r="O79" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -38216,7 +38261,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -38304,7 +38349,7 @@
         <v>6</v>
       </c>
       <c r="O80" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -38312,7 +38357,7 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R80" t="inlineStr">
         <is>
@@ -38400,7 +38445,7 @@
         <v>7</v>
       </c>
       <c r="O81" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -38408,7 +38453,7 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R81" t="inlineStr">
         <is>
@@ -38423,6 +38468,11 @@
       <c r="T81" t="inlineStr">
         <is>
           <t>Stange + Banner</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V81" t="n">
@@ -38529,7 +38579,7 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R83" t="inlineStr">
         <is>
@@ -38625,7 +38675,7 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R84" t="inlineStr">
         <is>
@@ -38721,7 +38771,7 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R85" t="inlineStr">
         <is>
@@ -38809,7 +38859,7 @@
         <v>4</v>
       </c>
       <c r="O86" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -38817,7 +38867,7 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R86" t="inlineStr">
         <is>
@@ -38905,7 +38955,7 @@
         <v>5</v>
       </c>
       <c r="O87" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -38913,7 +38963,7 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R87" t="inlineStr">
         <is>
@@ -39001,7 +39051,7 @@
         <v>6</v>
       </c>
       <c r="O88" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -39009,7 +39059,7 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R88" t="inlineStr">
         <is>
@@ -39097,7 +39147,7 @@
         <v>7</v>
       </c>
       <c r="O89" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -39105,7 +39155,7 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R89" t="inlineStr">
         <is>
@@ -39120,6 +39170,11 @@
       <c r="T89" t="inlineStr">
         <is>
           <t>Gefäß + Kette</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V89" t="n">
@@ -39226,7 +39281,7 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="R91" t="inlineStr">
         <is>
@@ -39322,7 +39377,7 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="R92" t="inlineStr">
         <is>
@@ -39418,7 +39473,7 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="R93" t="inlineStr">
         <is>
@@ -39506,7 +39561,7 @@
         <v>4</v>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -39514,7 +39569,7 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="R94" t="inlineStr">
         <is>
@@ -39602,7 +39657,7 @@
         <v>5</v>
       </c>
       <c r="O95" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -39610,7 +39665,7 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="R95" t="inlineStr">
         <is>
@@ -39698,7 +39753,7 @@
         <v>6</v>
       </c>
       <c r="O96" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -39706,7 +39761,7 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="R96" t="inlineStr">
         <is>
@@ -39794,7 +39849,7 @@
         <v>7</v>
       </c>
       <c r="O97" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -39802,7 +39857,7 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="R97" t="inlineStr">
         <is>
@@ -39817,6 +39872,11 @@
       <c r="T97" t="inlineStr">
         <is>
           <t>Kolben + Lockstoff</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
       <c r="V97" t="n">

--- a/data/itemliste_v7.xlsx
+++ b/data/itemliste_v7.xlsx
@@ -1309,7 +1309,7 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>8</v>
@@ -1417,7 +1417,7 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>10</v>
@@ -1525,7 +1525,7 @@
         <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>14</v>
@@ -1633,7 +1633,7 @@
         <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2094,7 +2094,7 @@
         <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>8</v>
@@ -2202,7 +2202,7 @@
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
         <v>10</v>
@@ -2310,7 +2310,7 @@
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
         <v>14</v>
@@ -2418,7 +2418,7 @@
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -2879,7 +2879,7 @@
         <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
         <v>10</v>
@@ -2987,7 +2987,7 @@
         <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
         <v>13</v>
@@ -3095,7 +3095,7 @@
         <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
         <v>17</v>
@@ -3203,7 +3203,7 @@
         <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -3664,7 +3664,7 @@
         <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
         <v>10</v>
@@ -3772,7 +3772,7 @@
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
         <v>13</v>
@@ -3880,7 +3880,7 @@
         <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
         <v>17</v>
@@ -3988,7 +3988,7 @@
         <v>7</v>
       </c>
       <c r="O33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -4449,7 +4449,7 @@
         <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
         <v>14</v>
@@ -4557,7 +4557,7 @@
         <v>5</v>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
         <v>18</v>
@@ -4665,7 +4665,7 @@
         <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
         <v>24</v>
@@ -4773,7 +4773,7 @@
         <v>7</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -5234,7 +5234,7 @@
         <v>4</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -5342,7 +5342,7 @@
         <v>5</v>
       </c>
       <c r="O47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -5450,7 +5450,7 @@
         <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -5558,7 +5558,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -6019,7 +6019,7 @@
         <v>4</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
         <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -6235,7 +6235,7 @@
         <v>6</v>
       </c>
       <c r="O56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>7</v>
       </c>
       <c r="O57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -6994,7 +6994,7 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -7105,7 +7105,7 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>6</v>
@@ -7216,7 +7216,7 @@
         <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>8</v>
@@ -7327,7 +7327,7 @@
         <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -7801,7 +7801,7 @@
         <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
@@ -7912,7 +7912,7 @@
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
         <v>6</v>
@@ -8023,7 +8023,7 @@
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
         <v>8</v>
@@ -8134,7 +8134,7 @@
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -8608,7 +8608,7 @@
         <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
         <v>6</v>
@@ -8719,7 +8719,7 @@
         <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
         <v>8</v>
@@ -8830,7 +8830,7 @@
         <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
         <v>10</v>
@@ -8941,7 +8941,7 @@
         <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -9415,7 +9415,7 @@
         <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
         <v>6</v>
@@ -9526,7 +9526,7 @@
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
         <v>8</v>
@@ -9637,7 +9637,7 @@
         <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
         <v>10</v>
@@ -9748,7 +9748,7 @@
         <v>7</v>
       </c>
       <c r="O33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -10222,7 +10222,7 @@
         <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
         <v>8</v>
@@ -10333,7 +10333,7 @@
         <v>5</v>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
         <v>11</v>
@@ -10444,7 +10444,7 @@
         <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
         <v>14</v>
@@ -10555,7 +10555,7 @@
         <v>7</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -11029,7 +11029,7 @@
         <v>4</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -11140,7 +11140,7 @@
         <v>5</v>
       </c>
       <c r="O47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -11251,7 +11251,7 @@
         <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -11362,7 +11362,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -11836,7 +11836,7 @@
         <v>4</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -11947,7 +11947,7 @@
         <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -12058,7 +12058,7 @@
         <v>6</v>
       </c>
       <c r="O56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -12169,7 +12169,7 @@
         <v>7</v>
       </c>
       <c r="O57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>
@@ -40477,7 +40477,7 @@
         <v>4</v>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
         <v>5</v>
@@ -40585,7 +40585,7 @@
         <v>5</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P7" t="n">
         <v>6</v>
@@ -40693,7 +40693,7 @@
         <v>6</v>
       </c>
       <c r="O8" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P8" t="n">
         <v>8</v>
@@ -40801,7 +40801,7 @@
         <v>7</v>
       </c>
       <c r="O9" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -41262,7 +41262,7 @@
         <v>4</v>
       </c>
       <c r="O14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
         <v>5</v>
@@ -41370,7 +41370,7 @@
         <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
         <v>6</v>
@@ -41478,7 +41478,7 @@
         <v>6</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P16" t="n">
         <v>8</v>
@@ -41586,7 +41586,7 @@
         <v>7</v>
       </c>
       <c r="O17" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -42047,7 +42047,7 @@
         <v>4</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P22" t="n">
         <v>6</v>
@@ -42155,7 +42155,7 @@
         <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
         <v>8</v>
@@ -42263,7 +42263,7 @@
         <v>6</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P24" t="n">
         <v>10</v>
@@ -42371,7 +42371,7 @@
         <v>7</v>
       </c>
       <c r="O25" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P25" t="n">
         <v>0</v>
@@ -42832,7 +42832,7 @@
         <v>4</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
         <v>6</v>
@@ -42940,7 +42940,7 @@
         <v>5</v>
       </c>
       <c r="O31" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P31" t="n">
         <v>8</v>
@@ -43048,7 +43048,7 @@
         <v>6</v>
       </c>
       <c r="O32" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P32" t="n">
         <v>10</v>
@@ -43156,7 +43156,7 @@
         <v>7</v>
       </c>
       <c r="O33" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
         <v>0</v>
@@ -43617,7 +43617,7 @@
         <v>4</v>
       </c>
       <c r="O38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P38" t="n">
         <v>8</v>
@@ -43725,7 +43725,7 @@
         <v>5</v>
       </c>
       <c r="O39" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P39" t="n">
         <v>11</v>
@@ -43833,7 +43833,7 @@
         <v>6</v>
       </c>
       <c r="O40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
         <v>14</v>
@@ -43941,7 +43941,7 @@
         <v>7</v>
       </c>
       <c r="O41" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
         <v>0</v>
@@ -44402,7 +44402,7 @@
         <v>4</v>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P46" t="n">
         <v>0</v>
@@ -44510,7 +44510,7 @@
         <v>5</v>
       </c>
       <c r="O47" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P47" t="n">
         <v>0</v>
@@ -44618,7 +44618,7 @@
         <v>6</v>
       </c>
       <c r="O48" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P48" t="n">
         <v>0</v>
@@ -44726,7 +44726,7 @@
         <v>7</v>
       </c>
       <c r="O49" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P49" t="n">
         <v>0</v>
@@ -45187,7 +45187,7 @@
         <v>4</v>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P54" t="n">
         <v>0</v>
@@ -45295,7 +45295,7 @@
         <v>5</v>
       </c>
       <c r="O55" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P55" t="n">
         <v>0</v>
@@ -45403,7 +45403,7 @@
         <v>6</v>
       </c>
       <c r="O56" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="P56" t="n">
         <v>0</v>
@@ -45511,7 +45511,7 @@
         <v>7</v>
       </c>
       <c r="O57" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P57" t="n">
         <v>0</v>

--- a/data/itemliste_v7.xlsx
+++ b/data/itemliste_v7.xlsx
@@ -726,7 +726,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z57"/>
+  <dimension ref="A1:Y57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -835,55 +835,50 @@
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>Rüstung (phys. flach)</t>
         </is>
       </c>
       <c r="Q1" s="4" t="inlineStr">
         <is>
-          <t>Rüstung (phys. flach)</t>
+          <t>Resistenz (mag. flach)</t>
         </is>
       </c>
       <c r="R1" s="4" t="inlineStr">
         <is>
-          <t>Resistenz (mag. flach)</t>
+          <t>VIT/LP-Bonus</t>
         </is>
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>VIT/LP-Bonus</t>
+          <t>Prim. Attr.</t>
         </is>
       </c>
       <c r="T1" s="4" t="inlineStr">
         <is>
-          <t>Prim. Attr.</t>
+          <t>Prim. Wert</t>
         </is>
       </c>
       <c r="U1" s="4" t="inlineStr">
         <is>
-          <t>Prim. Wert</t>
+          <t>Sek. Attr.</t>
         </is>
       </c>
       <c r="V1" s="4" t="inlineStr">
         <is>
-          <t>Sek. Attr.</t>
+          <t>Sek. Wert</t>
         </is>
       </c>
       <c r="W1" s="4" t="inlineStr">
         <is>
-          <t>Sek. Wert</t>
+          <t>Bauteile</t>
         </is>
       </c>
       <c r="X1" s="4" t="inlineStr">
         <is>
-          <t>Bauteile</t>
+          <t>Kaufpreis (Barren)</t>
         </is>
       </c>
       <c r="Y1" s="4" t="inlineStr">
-        <is>
-          <t>Kaufpreis (Barren)</t>
-        </is>
-      </c>
-      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>Verkaufspreis</t>
         </is>
@@ -919,7 +914,6 @@
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
-      <c r="Z2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -988,24 +982,26 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R3" t="n">
-        <v>6</v>
-      </c>
-      <c r="S3" t="n">
         <v>4</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U3" t="n">
-        <v>6</v>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -1014,18 +1010,13 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
           <t>Stoffbahn + Saum</t>
         </is>
       </c>
+      <c r="X3" t="n">
+        <v>10</v>
+      </c>
       <c r="Y3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1096,24 +1087,26 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="R4" t="n">
-        <v>11</v>
-      </c>
-      <c r="S4" t="n">
         <v>6</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U4" t="n">
-        <v>10</v>
+      <c r="T4" t="n">
+        <v>5</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -1122,18 +1115,13 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
           <t>Stoffbahn + Saum</t>
         </is>
       </c>
+      <c r="X4" t="n">
+        <v>20</v>
+      </c>
       <c r="Y4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1204,24 +1192,26 @@
         <v>3</v>
       </c>
       <c r="P5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q5" t="n">
         <v>6</v>
       </c>
-      <c r="Q5" t="n">
-        <v>2</v>
-      </c>
       <c r="R5" t="n">
-        <v>16</v>
-      </c>
-      <c r="S5" t="n">
         <v>8</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U5" t="n">
-        <v>14</v>
+      <c r="T5" t="n">
+        <v>7</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -1230,18 +1220,13 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
           <t>Stoffbahn + Saum</t>
         </is>
       </c>
+      <c r="X5" t="n">
+        <v>40</v>
+      </c>
       <c r="Y5" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -1312,24 +1297,26 @@
         <v>3</v>
       </c>
       <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
         <v>8</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3</v>
-      </c>
       <c r="R6" t="n">
-        <v>22</v>
-      </c>
-      <c r="S6" t="n">
         <v>12</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U6" t="n">
-        <v>20</v>
+      <c r="T6" t="n">
+        <v>10</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -1338,18 +1325,13 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
           <t>Stoffbahn + Saum</t>
         </is>
       </c>
+      <c r="X6" t="n">
+        <v>100</v>
+      </c>
       <c r="Y6" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z6" t="n">
         <v>60</v>
       </c>
     </row>
@@ -1420,24 +1402,26 @@
         <v>3</v>
       </c>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>10</v>
       </c>
-      <c r="Q7" t="n">
-        <v>4</v>
-      </c>
       <c r="R7" t="n">
-        <v>30</v>
-      </c>
-      <c r="S7" t="n">
         <v>16</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U7" t="n">
-        <v>27</v>
+      <c r="T7" t="n">
+        <v>13</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -1446,18 +1430,13 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
           <t>Stoffbahn + Saum</t>
         </is>
       </c>
+      <c r="X7" t="n">
+        <v>200</v>
+      </c>
       <c r="Y7" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z7" t="n">
         <v>120</v>
       </c>
     </row>
@@ -1528,24 +1507,26 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="R8" t="n">
-        <v>40</v>
-      </c>
-      <c r="S8" t="n">
         <v>21</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U8" t="n">
-        <v>35</v>
+      <c r="T8" t="n">
+        <v>17</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1554,18 +1535,13 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
           <t>Stoffbahn + Saum</t>
         </is>
       </c>
+      <c r="X8" t="n">
+        <v>500</v>
+      </c>
       <c r="Y8" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z8" t="n">
         <v>300</v>
       </c>
     </row>
@@ -1636,24 +1612,26 @@
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
+      <c r="T9" t="n">
+        <v>23</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1662,15 +1640,10 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
           <t>Stoffbahn + Saum</t>
         </is>
       </c>
-      <c r="Z9" t="n">
+      <c r="Y9" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -1704,7 +1677,6 @@
       <c r="W10" s="3" t="n"/>
       <c r="X10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
-      <c r="Z10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1776,21 +1748,23 @@
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R11" t="n">
-        <v>3</v>
-      </c>
-      <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U11" t="n">
-        <v>6</v>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1799,18 +1773,13 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Riemen</t>
         </is>
       </c>
+      <c r="X11" t="n">
+        <v>10</v>
+      </c>
       <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -1881,24 +1850,26 @@
         <v>2</v>
       </c>
       <c r="P12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>6</v>
-      </c>
-      <c r="S12" t="n">
         <v>8</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U12" t="n">
-        <v>10</v>
+      <c r="T12" t="n">
+        <v>5</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1907,18 +1878,13 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Riemen</t>
         </is>
       </c>
+      <c r="X12" t="n">
+        <v>20</v>
+      </c>
       <c r="Y12" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1989,24 +1955,26 @@
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R13" t="n">
-        <v>8</v>
-      </c>
-      <c r="S13" t="n">
         <v>11</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U13" t="n">
-        <v>14</v>
+      <c r="T13" t="n">
+        <v>7</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -2015,18 +1983,13 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Riemen</t>
         </is>
       </c>
+      <c r="X13" t="n">
+        <v>40</v>
+      </c>
       <c r="Y13" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z13" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2097,24 +2060,26 @@
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R14" t="n">
-        <v>11</v>
-      </c>
-      <c r="S14" t="n">
         <v>16</v>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U14" t="n">
-        <v>20</v>
+      <c r="T14" t="n">
+        <v>10</v>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -2123,18 +2088,13 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Riemen</t>
         </is>
       </c>
+      <c r="X14" t="n">
+        <v>100</v>
+      </c>
       <c r="Y14" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z14" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2205,24 +2165,26 @@
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q15" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R15" t="n">
-        <v>15</v>
-      </c>
-      <c r="S15" t="n">
         <v>22</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U15" t="n">
-        <v>27</v>
+      <c r="T15" t="n">
+        <v>13</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -2231,18 +2193,13 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Riemen</t>
         </is>
       </c>
+      <c r="X15" t="n">
+        <v>200</v>
+      </c>
       <c r="Y15" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z15" t="n">
         <v>120</v>
       </c>
     </row>
@@ -2313,24 +2270,26 @@
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="R16" t="n">
-        <v>20</v>
-      </c>
-      <c r="S16" t="n">
         <v>28</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U16" t="n">
-        <v>35</v>
+      <c r="T16" t="n">
+        <v>17</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -2339,18 +2298,13 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Riemen</t>
         </is>
       </c>
+      <c r="X16" t="n">
+        <v>500</v>
+      </c>
       <c r="Y16" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z16" t="n">
         <v>300</v>
       </c>
     </row>
@@ -2421,24 +2375,26 @@
         <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="inlineStr">
+        <v>38</v>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
+      <c r="T17" t="n">
+        <v>23</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -2447,15 +2403,10 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Riemen</t>
         </is>
       </c>
-      <c r="Z17" t="n">
+      <c r="Y17" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -2489,7 +2440,6 @@
       <c r="W18" s="3" t="n"/>
       <c r="X18" s="3" t="n"/>
       <c r="Y18" s="3" t="n"/>
-      <c r="Z18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2558,24 +2508,26 @@
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R19" t="n">
-        <v>4</v>
-      </c>
-      <c r="S19" t="n">
         <v>6</v>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="U19" t="n">
-        <v>6</v>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -2584,18 +2536,13 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
           <t>Kettengeflecht</t>
         </is>
       </c>
+      <c r="X19" t="n">
+        <v>10</v>
+      </c>
       <c r="Y19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -2666,24 +2613,26 @@
         <v>2</v>
       </c>
       <c r="P20" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>10</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
         <v>5</v>
       </c>
-      <c r="Q20" t="n">
-        <v>7</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7</v>
-      </c>
-      <c r="S20" t="n">
-        <v>10</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>VIT</t>
-        </is>
-      </c>
-      <c r="U20" t="n">
-        <v>10</v>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -2692,18 +2641,13 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
           <t>Kettengeflecht</t>
         </is>
       </c>
+      <c r="X20" t="n">
+        <v>20</v>
+      </c>
       <c r="Y20" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z20" t="n">
         <v>12</v>
       </c>
     </row>
@@ -2774,24 +2718,26 @@
         <v>3</v>
       </c>
       <c r="P21" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>4</v>
+      </c>
+      <c r="R21" t="n">
+        <v>14</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
         <v>7</v>
       </c>
-      <c r="Q21" t="n">
-        <v>10</v>
-      </c>
-      <c r="R21" t="n">
-        <v>10</v>
-      </c>
-      <c r="S21" t="n">
-        <v>14</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>VIT</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>14</v>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2800,18 +2746,13 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
           <t>Kettengeflecht</t>
         </is>
       </c>
+      <c r="X21" t="n">
+        <v>40</v>
+      </c>
       <c r="Y21" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z21" t="n">
         <v>24</v>
       </c>
     </row>
@@ -2882,24 +2823,26 @@
         <v>3</v>
       </c>
       <c r="P22" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>5</v>
+      </c>
+      <c r="R22" t="n">
+        <v>20</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
         <v>10</v>
       </c>
-      <c r="Q22" t="n">
-        <v>14</v>
-      </c>
-      <c r="R22" t="n">
-        <v>14</v>
-      </c>
-      <c r="S22" t="n">
-        <v>20</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>VIT</t>
-        </is>
-      </c>
-      <c r="U22" t="n">
-        <v>20</v>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2908,18 +2851,13 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
           <t>Kettengeflecht</t>
         </is>
       </c>
+      <c r="X22" t="n">
+        <v>100</v>
+      </c>
       <c r="Y22" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -2990,24 +2928,26 @@
         <v>3</v>
       </c>
       <c r="P23" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>6</v>
+      </c>
+      <c r="R23" t="n">
+        <v>27</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
         <v>13</v>
       </c>
-      <c r="Q23" t="n">
-        <v>19</v>
-      </c>
-      <c r="R23" t="n">
-        <v>19</v>
-      </c>
-      <c r="S23" t="n">
-        <v>27</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>VIT</t>
-        </is>
-      </c>
-      <c r="U23" t="n">
-        <v>27</v>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -3016,18 +2956,13 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
           <t>Kettengeflecht</t>
         </is>
       </c>
+      <c r="X23" t="n">
+        <v>200</v>
+      </c>
       <c r="Y23" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z23" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3098,24 +3033,26 @@
         <v>3</v>
       </c>
       <c r="P24" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>8</v>
+      </c>
+      <c r="R24" t="n">
+        <v>35</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
         <v>17</v>
       </c>
-      <c r="Q24" t="n">
-        <v>25</v>
-      </c>
-      <c r="R24" t="n">
-        <v>25</v>
-      </c>
-      <c r="S24" t="n">
-        <v>35</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>VIT</t>
-        </is>
-      </c>
-      <c r="U24" t="n">
-        <v>35</v>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -3124,18 +3061,13 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
           <t>Kettengeflecht</t>
         </is>
       </c>
+      <c r="X24" t="n">
+        <v>500</v>
+      </c>
       <c r="Y24" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z24" t="n">
         <v>300</v>
       </c>
     </row>
@@ -3206,24 +3138,26 @@
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="inlineStr">
+        <v>47</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
+      <c r="T25" t="n">
+        <v>23</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -3232,15 +3166,10 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
           <t>Kettengeflecht</t>
         </is>
       </c>
-      <c r="Z25" t="n">
+      <c r="Y25" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -3274,7 +3203,6 @@
       <c r="W26" s="3" t="n"/>
       <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="n"/>
-      <c r="Z26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3346,21 +3274,23 @@
         <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R27" t="n">
-        <v>2</v>
-      </c>
-      <c r="S27" t="n">
         <v>7</v>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="U27" t="n">
-        <v>6</v>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -3369,18 +3299,13 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
           <t>Schuppen + Unterzeug</t>
         </is>
       </c>
+      <c r="X27" t="n">
+        <v>10</v>
+      </c>
       <c r="Y27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z27" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3451,24 +3376,26 @@
         <v>2</v>
       </c>
       <c r="P28" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>11</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T28" t="n">
         <v>5</v>
       </c>
-      <c r="Q28" t="n">
-        <v>10</v>
-      </c>
-      <c r="R28" t="n">
-        <v>4</v>
-      </c>
-      <c r="S28" t="n">
-        <v>11</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U28" t="n">
-        <v>10</v>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -3477,18 +3404,13 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
           <t>Schuppen + Unterzeug</t>
         </is>
       </c>
+      <c r="X28" t="n">
+        <v>20</v>
+      </c>
       <c r="Y28" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z28" t="n">
         <v>12</v>
       </c>
     </row>
@@ -3559,24 +3481,26 @@
         <v>3</v>
       </c>
       <c r="P29" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>15</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
         <v>7</v>
       </c>
-      <c r="Q29" t="n">
-        <v>14</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6</v>
-      </c>
-      <c r="S29" t="n">
-        <v>15</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U29" t="n">
-        <v>14</v>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -3585,18 +3509,13 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
           <t>Schuppen + Unterzeug</t>
         </is>
       </c>
+      <c r="X29" t="n">
+        <v>40</v>
+      </c>
       <c r="Y29" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z29" t="n">
         <v>24</v>
       </c>
     </row>
@@ -3667,24 +3586,26 @@
         <v>3</v>
       </c>
       <c r="P30" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3</v>
+      </c>
+      <c r="R30" t="n">
+        <v>22</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
         <v>10</v>
       </c>
-      <c r="Q30" t="n">
-        <v>20</v>
-      </c>
-      <c r="R30" t="n">
-        <v>8</v>
-      </c>
-      <c r="S30" t="n">
-        <v>22</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U30" t="n">
-        <v>20</v>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -3693,18 +3614,13 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
           <t>Schuppen + Unterzeug</t>
         </is>
       </c>
+      <c r="X30" t="n">
+        <v>100</v>
+      </c>
       <c r="Y30" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z30" t="n">
         <v>60</v>
       </c>
     </row>
@@ -3775,24 +3691,26 @@
         <v>3</v>
       </c>
       <c r="P31" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>4</v>
+      </c>
+      <c r="R31" t="n">
+        <v>30</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
         <v>13</v>
       </c>
-      <c r="Q31" t="n">
-        <v>27</v>
-      </c>
-      <c r="R31" t="n">
-        <v>11</v>
-      </c>
-      <c r="S31" t="n">
-        <v>30</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U31" t="n">
-        <v>27</v>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -3801,18 +3719,13 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
           <t>Schuppen + Unterzeug</t>
         </is>
       </c>
+      <c r="X31" t="n">
+        <v>200</v>
+      </c>
       <c r="Y31" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z31" t="n">
         <v>120</v>
       </c>
     </row>
@@ -3883,24 +3796,26 @@
         <v>3</v>
       </c>
       <c r="P32" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>39</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
         <v>17</v>
       </c>
-      <c r="Q32" t="n">
-        <v>35</v>
-      </c>
-      <c r="R32" t="n">
-        <v>15</v>
-      </c>
-      <c r="S32" t="n">
-        <v>38</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U32" t="n">
-        <v>35</v>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -3909,18 +3824,13 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
           <t>Schuppen + Unterzeug</t>
         </is>
       </c>
+      <c r="X32" t="n">
+        <v>500</v>
+      </c>
       <c r="Y32" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z32" t="n">
         <v>300</v>
       </c>
     </row>
@@ -3991,24 +3901,26 @@
         <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="inlineStr">
+        <v>52</v>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
+      <c r="T33" t="n">
+        <v>23</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -4017,15 +3929,10 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
           <t>Schuppen + Unterzeug</t>
         </is>
       </c>
-      <c r="Z33" t="n">
+      <c r="Y33" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -4059,7 +3966,6 @@
       <c r="W34" s="3" t="n"/>
       <c r="X34" s="3" t="n"/>
       <c r="Y34" s="3" t="n"/>
-      <c r="Z34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4128,24 +4034,26 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q35" t="n">
+        <v>1</v>
+      </c>
+      <c r="R35" t="n">
         <v>7</v>
       </c>
-      <c r="R35" t="n">
-        <v>3</v>
-      </c>
-      <c r="S35" t="n">
-        <v>7</v>
-      </c>
-      <c r="T35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="U35" t="n">
-        <v>6</v>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -4154,18 +4062,13 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
           <t>Brustplatte + Schnallen</t>
         </is>
       </c>
+      <c r="X35" t="n">
+        <v>10</v>
+      </c>
       <c r="Y35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -4236,24 +4139,26 @@
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Q36" t="n">
+        <v>2</v>
+      </c>
+      <c r="R36" t="n">
         <v>12</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
         <v>5</v>
       </c>
-      <c r="S36" t="n">
-        <v>12</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
-      <c r="U36" t="n">
-        <v>10</v>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -4262,18 +4167,13 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
           <t>Brustplatte + Schnallen</t>
         </is>
       </c>
+      <c r="X36" t="n">
+        <v>20</v>
+      </c>
       <c r="Y36" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z36" t="n">
         <v>12</v>
       </c>
     </row>
@@ -4344,24 +4244,26 @@
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q37" t="n">
+        <v>3</v>
+      </c>
+      <c r="R37" t="n">
         <v>17</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
         <v>7</v>
       </c>
-      <c r="S37" t="n">
-        <v>17</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
-      <c r="U37" t="n">
-        <v>14</v>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -4370,18 +4272,13 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
           <t>Brustplatte + Schnallen</t>
         </is>
       </c>
+      <c r="X37" t="n">
+        <v>40</v>
+      </c>
       <c r="Y37" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z37" t="n">
         <v>24</v>
       </c>
     </row>
@@ -4452,24 +4349,26 @@
         <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q38" t="n">
+        <v>4</v>
+      </c>
+      <c r="R38" t="n">
         <v>24</v>
       </c>
-      <c r="R38" t="n">
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="T38" t="n">
         <v>10</v>
       </c>
-      <c r="S38" t="n">
-        <v>24</v>
-      </c>
-      <c r="T38" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
-      <c r="U38" t="n">
-        <v>20</v>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -4478,18 +4377,13 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
           <t>Brustplatte + Schnallen</t>
         </is>
       </c>
+      <c r="X38" t="n">
+        <v>100</v>
+      </c>
       <c r="Y38" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z38" t="n">
         <v>60</v>
       </c>
     </row>
@@ -4560,24 +4454,26 @@
         <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="Q39" t="n">
+        <v>4</v>
+      </c>
+      <c r="R39" t="n">
         <v>32</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="T39" t="n">
         <v>13</v>
       </c>
-      <c r="S39" t="n">
-        <v>32</v>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
-      <c r="U39" t="n">
-        <v>27</v>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -4586,18 +4482,13 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
           <t>Brustplatte + Schnallen</t>
         </is>
       </c>
+      <c r="X39" t="n">
+        <v>200</v>
+      </c>
       <c r="Y39" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z39" t="n">
         <v>120</v>
       </c>
     </row>
@@ -4668,24 +4559,26 @@
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="Q40" t="n">
+        <v>6</v>
+      </c>
+      <c r="R40" t="n">
         <v>42</v>
       </c>
-      <c r="R40" t="n">
-        <v>18</v>
-      </c>
-      <c r="S40" t="n">
-        <v>42</v>
-      </c>
-      <c r="T40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="U40" t="n">
-        <v>35</v>
+      <c r="T40" t="n">
+        <v>17</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -4694,18 +4587,13 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
           <t>Brustplatte + Schnallen</t>
         </is>
       </c>
+      <c r="X40" t="n">
+        <v>500</v>
+      </c>
       <c r="Y40" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z40" t="n">
         <v>300</v>
       </c>
     </row>
@@ -4776,24 +4664,26 @@
         <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="inlineStr">
+        <v>56</v>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
+      <c r="T41" t="n">
+        <v>23</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -4802,15 +4692,10 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
           <t>Brustplatte + Schnallen</t>
         </is>
       </c>
-      <c r="Z41" t="n">
+      <c r="Y41" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -4844,7 +4729,6 @@
       <c r="W42" s="3" t="n"/>
       <c r="X42" s="3" t="n"/>
       <c r="Y42" s="3" t="n"/>
-      <c r="Z42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4921,16 +4805,18 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U43" t="n">
-        <v>6</v>
+      <c r="T43" t="n">
+        <v>3</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -4939,18 +4825,13 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
           <t>Lederköcher + Trageriemen</t>
         </is>
       </c>
+      <c r="X43" t="n">
+        <v>10</v>
+      </c>
       <c r="Y43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z43" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5029,16 +4910,18 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U44" t="n">
-        <v>10</v>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -5047,18 +4930,13 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
           <t>Lederköcher + Trageriemen</t>
         </is>
       </c>
+      <c r="X44" t="n">
+        <v>20</v>
+      </c>
       <c r="Y44" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z44" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5137,16 +5015,18 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U45" t="n">
-        <v>14</v>
+      <c r="T45" t="n">
+        <v>7</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -5155,18 +5035,13 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
           <t>Lederköcher + Trageriemen</t>
         </is>
       </c>
+      <c r="X45" t="n">
+        <v>40</v>
+      </c>
       <c r="Y45" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z45" t="n">
         <v>24</v>
       </c>
     </row>
@@ -5245,16 +5120,18 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U46" t="n">
-        <v>20</v>
+      <c r="T46" t="n">
+        <v>10</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -5263,18 +5140,13 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
           <t>Lederköcher + Trageriemen</t>
         </is>
       </c>
+      <c r="X46" t="n">
+        <v>100</v>
+      </c>
       <c r="Y46" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z46" t="n">
         <v>60</v>
       </c>
     </row>
@@ -5353,16 +5225,18 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U47" t="n">
-        <v>27</v>
+      <c r="T47" t="n">
+        <v>13</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -5371,18 +5245,13 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
           <t>Lederköcher + Trageriemen</t>
         </is>
       </c>
+      <c r="X47" t="n">
+        <v>200</v>
+      </c>
       <c r="Y47" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z47" t="n">
         <v>120</v>
       </c>
     </row>
@@ -5461,16 +5330,18 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U48" t="n">
-        <v>35</v>
+      <c r="T48" t="n">
+        <v>17</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -5479,18 +5350,13 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
           <t>Lederköcher + Trageriemen</t>
         </is>
       </c>
+      <c r="X48" t="n">
+        <v>500</v>
+      </c>
       <c r="Y48" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z48" t="n">
         <v>300</v>
       </c>
     </row>
@@ -5569,16 +5435,18 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U49" t="n">
-        <v>0</v>
+      <c r="T49" t="n">
+        <v>23</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -5587,15 +5455,10 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
           <t>Lederköcher + Trageriemen</t>
         </is>
       </c>
-      <c r="Z49" t="n">
+      <c r="Y49" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -5629,7 +5492,6 @@
       <c r="W50" s="3" t="n"/>
       <c r="X50" s="3" t="n"/>
       <c r="Y50" s="3" t="n"/>
-      <c r="Z50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5706,16 +5568,18 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U51" t="n">
-        <v>6</v>
+      <c r="T51" t="n">
+        <v>3</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -5724,18 +5588,13 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
           <t>Pergament + Wickelstäbe</t>
         </is>
       </c>
+      <c r="X51" t="n">
+        <v>10</v>
+      </c>
       <c r="Y51" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z51" t="n">
         <v>6</v>
       </c>
     </row>
@@ -5814,16 +5673,18 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U52" t="n">
-        <v>10</v>
+      <c r="T52" t="n">
+        <v>5</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -5832,18 +5693,13 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
           <t>Pergament + Wickelstäbe</t>
         </is>
       </c>
+      <c r="X52" t="n">
+        <v>20</v>
+      </c>
       <c r="Y52" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z52" t="n">
         <v>12</v>
       </c>
     </row>
@@ -5922,16 +5778,18 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U53" t="n">
-        <v>14</v>
+      <c r="T53" t="n">
+        <v>7</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -5940,18 +5798,13 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
           <t>Pergament + Wickelstäbe</t>
         </is>
       </c>
+      <c r="X53" t="n">
+        <v>40</v>
+      </c>
       <c r="Y53" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z53" t="n">
         <v>24</v>
       </c>
     </row>
@@ -6030,16 +5883,18 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U54" t="n">
-        <v>20</v>
+      <c r="T54" t="n">
+        <v>10</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -6048,18 +5903,13 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
           <t>Pergament + Wickelstäbe</t>
         </is>
       </c>
+      <c r="X54" t="n">
+        <v>100</v>
+      </c>
       <c r="Y54" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z54" t="n">
         <v>60</v>
       </c>
     </row>
@@ -6138,16 +5988,18 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U55" t="n">
-        <v>27</v>
+      <c r="T55" t="n">
+        <v>13</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -6156,18 +6008,13 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
           <t>Pergament + Wickelstäbe</t>
         </is>
       </c>
+      <c r="X55" t="n">
+        <v>200</v>
+      </c>
       <c r="Y55" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z55" t="n">
         <v>120</v>
       </c>
     </row>
@@ -6246,16 +6093,18 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U56" t="n">
-        <v>35</v>
+      <c r="T56" t="n">
+        <v>17</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -6264,18 +6113,13 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
           <t>Pergament + Wickelstäbe</t>
         </is>
       </c>
+      <c r="X56" t="n">
+        <v>500</v>
+      </c>
       <c r="Y56" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z56" t="n">
         <v>300</v>
       </c>
     </row>
@@ -6354,16 +6198,18 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U57" t="n">
-        <v>0</v>
+      <c r="T57" t="n">
+        <v>23</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -6372,15 +6218,10 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
           <t>Pergament + Wickelstäbe</t>
         </is>
       </c>
-      <c r="Z57" t="n">
+      <c r="Y57" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -6395,7 +6236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA57"/>
+  <dimension ref="A1:Z57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -6505,60 +6346,55 @@
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>Rüstung (phys. flach)</t>
         </is>
       </c>
       <c r="Q1" s="4" t="inlineStr">
         <is>
-          <t>Rüstung (phys. flach)</t>
+          <t>Resistenz (mag. flach)</t>
         </is>
       </c>
       <c r="R1" s="4" t="inlineStr">
         <is>
-          <t>Resistenz (mag. flach)</t>
+          <t>VIT/LP-Bonus</t>
         </is>
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>VIT/LP-Bonus</t>
+          <t>MOB-Bonus</t>
         </is>
       </c>
       <c r="T1" s="4" t="inlineStr">
         <is>
-          <t>MOB-Bonus</t>
+          <t>Prim. Attr.</t>
         </is>
       </c>
       <c r="U1" s="4" t="inlineStr">
         <is>
-          <t>Prim. Attr.</t>
+          <t>Prim. Wert</t>
         </is>
       </c>
       <c r="V1" s="4" t="inlineStr">
         <is>
-          <t>Prim. Wert</t>
+          <t>Sek. Attr.</t>
         </is>
       </c>
       <c r="W1" s="4" t="inlineStr">
         <is>
-          <t>Sek. Attr.</t>
+          <t>Sek. Wert</t>
         </is>
       </c>
       <c r="X1" s="4" t="inlineStr">
         <is>
-          <t>Sek. Wert</t>
+          <t>Bauteile</t>
         </is>
       </c>
       <c r="Y1" s="4" t="inlineStr">
         <is>
-          <t>Bauteile</t>
+          <t>Kaufpreis (Barren)</t>
         </is>
       </c>
       <c r="Z1" s="4" t="inlineStr">
-        <is>
-          <t>Kaufpreis (Barren)</t>
-        </is>
-      </c>
-      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>Verkaufspreis</t>
         </is>
@@ -6595,7 +6431,6 @@
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
       <c r="Z2" s="3" t="n"/>
-      <c r="AA2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -6664,27 +6499,29 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
+        <v>2</v>
+      </c>
+      <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>WIL</t>
+        </is>
+      </c>
+      <c r="U3" t="n">
         <v>2</v>
       </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>WIL</t>
-        </is>
-      </c>
-      <c r="V3" t="n">
-        <v>3</v>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
@@ -6693,18 +6530,13 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
           <t>Sohle + Riemen</t>
         </is>
       </c>
+      <c r="Y3" t="n">
+        <v>10</v>
+      </c>
       <c r="Z3" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -6775,27 +6607,29 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="S4" t="n">
-        <v>4</v>
-      </c>
-      <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="V4" t="n">
-        <v>5</v>
+      <c r="U4" t="n">
+        <v>3</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
@@ -6804,18 +6638,13 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
           <t>Sohle + Riemen</t>
         </is>
       </c>
+      <c r="Y4" t="n">
+        <v>20</v>
+      </c>
       <c r="Z4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -6886,27 +6715,29 @@
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
-      </c>
-      <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="V5" t="n">
-        <v>7</v>
+      <c r="U5" t="n">
+        <v>4</v>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
@@ -6915,18 +6746,13 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
           <t>Sohle + Riemen</t>
         </is>
       </c>
+      <c r="Y5" t="n">
+        <v>40</v>
+      </c>
       <c r="Z5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -6997,27 +6823,29 @@
         <v>3</v>
       </c>
       <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
       <c r="R6" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="S6" t="n">
-        <v>7</v>
-      </c>
-      <c r="T6" t="n">
         <v>0</v>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="V6" t="n">
-        <v>10</v>
+      <c r="U6" t="n">
+        <v>5</v>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
@@ -7026,18 +6854,13 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
           <t>Sohle + Riemen</t>
         </is>
       </c>
+      <c r="Y6" t="n">
+        <v>100</v>
+      </c>
       <c r="Z6" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA6" t="n">
         <v>60</v>
       </c>
     </row>
@@ -7108,27 +6931,29 @@
         <v>3</v>
       </c>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
       <c r="R7" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="n">
         <v>0</v>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="V7" t="n">
-        <v>14</v>
+      <c r="U7" t="n">
+        <v>7</v>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
@@ -7137,18 +6962,13 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
           <t>Sohle + Riemen</t>
         </is>
       </c>
+      <c r="Y7" t="n">
+        <v>200</v>
+      </c>
       <c r="Z7" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA7" t="n">
         <v>120</v>
       </c>
     </row>
@@ -7219,27 +7039,29 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
       <c r="R8" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="S8" t="n">
-        <v>13</v>
-      </c>
-      <c r="T8" t="n">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="V8" t="n">
-        <v>18</v>
+      <c r="U8" t="n">
+        <v>9</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
@@ -7248,18 +7070,13 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
           <t>Sohle + Riemen</t>
         </is>
       </c>
+      <c r="Y8" t="n">
+        <v>500</v>
+      </c>
       <c r="Z8" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA8" t="n">
         <v>300</v>
       </c>
     </row>
@@ -7330,27 +7147,29 @@
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="V9" t="n">
-        <v>0</v>
+      <c r="U9" t="n">
+        <v>12</v>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -7359,15 +7178,10 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
           <t>Sohle + Riemen</t>
         </is>
       </c>
-      <c r="AA9" t="n">
+      <c r="Z9" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -7402,7 +7216,6 @@
       <c r="X10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
       <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -7471,27 +7284,29 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>GES</t>
+        </is>
+      </c>
+      <c r="U11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>GES</t>
-        </is>
-      </c>
-      <c r="V11" t="n">
-        <v>3</v>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
@@ -7500,18 +7315,13 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Schnürung</t>
         </is>
       </c>
+      <c r="Y11" t="n">
+        <v>10</v>
+      </c>
       <c r="Z11" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -7585,24 +7395,26 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T12" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V12" t="n">
-        <v>5</v>
+      <c r="U12" t="n">
+        <v>3</v>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
@@ -7611,18 +7423,13 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Schnürung</t>
         </is>
       </c>
+      <c r="Y12" t="n">
+        <v>20</v>
+      </c>
       <c r="Z12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -7693,27 +7500,29 @@
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S13" t="n">
-        <v>6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T13" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V13" t="n">
-        <v>7</v>
+      <c r="U13" t="n">
+        <v>4</v>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
@@ -7722,18 +7531,13 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Schnürung</t>
         </is>
       </c>
+      <c r="Y13" t="n">
+        <v>40</v>
+      </c>
       <c r="Z13" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA13" t="n">
         <v>24</v>
       </c>
     </row>
@@ -7804,27 +7608,29 @@
         <v>3</v>
       </c>
       <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>GES</t>
+        </is>
+      </c>
+      <c r="U14" t="n">
         <v>5</v>
       </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>GES</t>
-        </is>
-      </c>
-      <c r="V14" t="n">
-        <v>10</v>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
@@ -7833,18 +7639,13 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Schnürung</t>
         </is>
       </c>
+      <c r="Y14" t="n">
+        <v>100</v>
+      </c>
       <c r="Z14" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA14" t="n">
         <v>60</v>
       </c>
     </row>
@@ -7915,27 +7716,29 @@
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="S15" t="n">
-        <v>13</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V15" t="n">
-        <v>14</v>
+      <c r="U15" t="n">
+        <v>7</v>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
@@ -7944,18 +7747,13 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Schnürung</t>
         </is>
       </c>
+      <c r="Y15" t="n">
+        <v>200</v>
+      </c>
       <c r="Z15" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA15" t="n">
         <v>120</v>
       </c>
     </row>
@@ -8026,27 +7824,29 @@
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="S16" t="n">
-        <v>17</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V16" t="n">
-        <v>18</v>
+      <c r="U16" t="n">
+        <v>9</v>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
@@ -8055,18 +7855,13 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Schnürung</t>
         </is>
       </c>
+      <c r="Y16" t="n">
+        <v>500</v>
+      </c>
       <c r="Z16" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA16" t="n">
         <v>300</v>
       </c>
     </row>
@@ -8137,27 +7932,29 @@
         <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V17" t="n">
-        <v>0</v>
+      <c r="U17" t="n">
+        <v>12</v>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
@@ -8166,15 +7963,10 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
           <t>Gegerbtes Leder + Schnürung</t>
         </is>
       </c>
-      <c r="AA17" t="n">
+      <c r="Z17" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -8209,7 +8001,6 @@
       <c r="X18" s="3" t="n"/>
       <c r="Y18" s="3" t="n"/>
       <c r="Z18" s="3" t="n"/>
-      <c r="AA18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -8278,27 +8069,29 @@
         <v>1</v>
       </c>
       <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>VIT</t>
-        </is>
-      </c>
-      <c r="V19" t="n">
-        <v>3</v>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
@@ -8307,18 +8100,13 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Sohle</t>
         </is>
       </c>
+      <c r="Y19" t="n">
+        <v>10</v>
+      </c>
       <c r="Z19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -8389,27 +8177,29 @@
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="S20" t="n">
-        <v>6</v>
-      </c>
-      <c r="T20" t="n">
         <v>0</v>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="V20" t="n">
-        <v>5</v>
+      <c r="U20" t="n">
+        <v>3</v>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
@@ -8418,18 +8208,13 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Sohle</t>
         </is>
       </c>
+      <c r="Y20" t="n">
+        <v>20</v>
+      </c>
       <c r="Z20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA20" t="n">
         <v>12</v>
       </c>
     </row>
@@ -8500,27 +8285,29 @@
         <v>3</v>
       </c>
       <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>8</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="U21" t="n">
         <v>4</v>
       </c>
-      <c r="Q21" t="n">
-        <v>6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>8</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>VIT</t>
-        </is>
-      </c>
-      <c r="V21" t="n">
-        <v>7</v>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
@@ -8529,18 +8316,13 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Sohle</t>
         </is>
       </c>
+      <c r="Y21" t="n">
+        <v>40</v>
+      </c>
       <c r="Z21" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA21" t="n">
         <v>24</v>
       </c>
     </row>
@@ -8611,27 +8393,29 @@
         <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="S22" t="n">
-        <v>12</v>
-      </c>
-      <c r="T22" t="n">
         <v>0</v>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="V22" t="n">
-        <v>10</v>
+      <c r="U22" t="n">
+        <v>5</v>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
@@ -8640,18 +8424,13 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Sohle</t>
         </is>
       </c>
+      <c r="Y22" t="n">
+        <v>100</v>
+      </c>
       <c r="Z22" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -8722,27 +8501,29 @@
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="S23" t="n">
-        <v>16</v>
-      </c>
-      <c r="T23" t="n">
         <v>0</v>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="V23" t="n">
-        <v>14</v>
+      <c r="U23" t="n">
+        <v>7</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
@@ -8751,18 +8532,13 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Sohle</t>
         </is>
       </c>
+      <c r="Y23" t="n">
+        <v>200</v>
+      </c>
       <c r="Z23" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA23" t="n">
         <v>120</v>
       </c>
     </row>
@@ -8833,27 +8609,29 @@
         <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="S24" t="n">
-        <v>21</v>
-      </c>
-      <c r="T24" t="n">
         <v>0</v>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="V24" t="n">
-        <v>18</v>
+      <c r="U24" t="n">
+        <v>9</v>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
@@ -8862,18 +8640,13 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Sohle</t>
         </is>
       </c>
+      <c r="Y24" t="n">
+        <v>500</v>
+      </c>
       <c r="Z24" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA24" t="n">
         <v>300</v>
       </c>
     </row>
@@ -8944,27 +8717,29 @@
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
-      <c r="T25" t="n">
-        <v>0</v>
-      </c>
-      <c r="U25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="V25" t="n">
-        <v>0</v>
+      <c r="U25" t="n">
+        <v>12</v>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
@@ -8973,15 +8748,10 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Sohle</t>
         </is>
       </c>
-      <c r="AA25" t="n">
+      <c r="Z25" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -9016,7 +8786,6 @@
       <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="n"/>
       <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -9085,27 +8854,29 @@
         <v>1</v>
       </c>
       <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="U27" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="V27" t="n">
-        <v>3</v>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
@@ -9114,18 +8885,13 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
           <t>Schuppen + Sohle</t>
         </is>
       </c>
+      <c r="Y27" t="n">
+        <v>10</v>
+      </c>
       <c r="Z27" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA27" t="n">
         <v>6</v>
       </c>
     </row>
@@ -9199,24 +8965,26 @@
         <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="S28" t="n">
-        <v>7</v>
-      </c>
-      <c r="T28" t="n">
         <v>0</v>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="V28" t="n">
-        <v>5</v>
+      <c r="U28" t="n">
+        <v>3</v>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
@@ -9225,18 +8993,13 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
           <t>Schuppen + Sohle</t>
         </is>
       </c>
+      <c r="Y28" t="n">
+        <v>20</v>
+      </c>
       <c r="Z28" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA28" t="n">
         <v>12</v>
       </c>
     </row>
@@ -9307,27 +9070,29 @@
         <v>3</v>
       </c>
       <c r="P29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>9</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="U29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>9</v>
-      </c>
-      <c r="T29" t="n">
-        <v>0</v>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="V29" t="n">
-        <v>7</v>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
@@ -9336,18 +9101,13 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
           <t>Schuppen + Sohle</t>
         </is>
       </c>
+      <c r="Y29" t="n">
+        <v>40</v>
+      </c>
       <c r="Z29" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA29" t="n">
         <v>24</v>
       </c>
     </row>
@@ -9418,27 +9178,29 @@
         <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
+        <v>13</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="U30" t="n">
         <v>5</v>
       </c>
-      <c r="S30" t="n">
-        <v>13</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="V30" t="n">
-        <v>10</v>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
@@ -9447,18 +9209,13 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
           <t>Schuppen + Sohle</t>
         </is>
       </c>
+      <c r="Y30" t="n">
+        <v>100</v>
+      </c>
       <c r="Z30" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA30" t="n">
         <v>60</v>
       </c>
     </row>
@@ -9529,27 +9286,29 @@
         <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
+        <v>18</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="U31" t="n">
         <v>7</v>
       </c>
-      <c r="S31" t="n">
-        <v>18</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="V31" t="n">
-        <v>14</v>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
@@ -9558,18 +9317,13 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
           <t>Schuppen + Sohle</t>
         </is>
       </c>
+      <c r="Y31" t="n">
+        <v>200</v>
+      </c>
       <c r="Z31" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA31" t="n">
         <v>120</v>
       </c>
     </row>
@@ -9640,27 +9394,29 @@
         <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
+        <v>23</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="U32" t="n">
         <v>9</v>
       </c>
-      <c r="S32" t="n">
-        <v>23</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="V32" t="n">
-        <v>18</v>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
@@ -9669,18 +9425,13 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
           <t>Schuppen + Sohle</t>
         </is>
       </c>
+      <c r="Y32" t="n">
+        <v>500</v>
+      </c>
       <c r="Z32" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA32" t="n">
         <v>300</v>
       </c>
     </row>
@@ -9751,27 +9502,29 @@
         <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
       </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="V33" t="n">
-        <v>0</v>
+      <c r="U33" t="n">
+        <v>12</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
@@ -9780,15 +9533,10 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
           <t>Schuppen + Sohle</t>
         </is>
       </c>
-      <c r="AA33" t="n">
+      <c r="Z33" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -9823,7 +9571,6 @@
       <c r="X34" s="3" t="n"/>
       <c r="Y34" s="3" t="n"/>
       <c r="Z34" s="3" t="n"/>
-      <c r="AA34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -9892,27 +9639,29 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="S35" t="n">
-        <v>5</v>
-      </c>
-      <c r="T35" t="n">
         <v>0</v>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="V35" t="n">
-        <v>3</v>
+      <c r="U35" t="n">
+        <v>2</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
@@ -9921,18 +9670,13 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
           <t>Stahlkappe + Schienen</t>
         </is>
       </c>
+      <c r="Y35" t="n">
+        <v>10</v>
+      </c>
       <c r="Z35" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10003,27 +9747,29 @@
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
         <v>7</v>
       </c>
-      <c r="R36" t="n">
-        <v>3</v>
-      </c>
       <c r="S36" t="n">
-        <v>7</v>
-      </c>
-      <c r="T36" t="n">
         <v>0</v>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="V36" t="n">
-        <v>5</v>
+      <c r="U36" t="n">
+        <v>3</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
@@ -10032,18 +9778,13 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
           <t>Stahlkappe + Schienen</t>
         </is>
       </c>
+      <c r="Y36" t="n">
+        <v>20</v>
+      </c>
       <c r="Z36" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA36" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10114,27 +9855,29 @@
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
         <v>10</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
         <v>4</v>
       </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="n">
-        <v>0</v>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
-      <c r="V37" t="n">
-        <v>7</v>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
@@ -10143,18 +9886,13 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
           <t>Stahlkappe + Schienen</t>
         </is>
       </c>
+      <c r="Y37" t="n">
+        <v>40</v>
+      </c>
       <c r="Z37" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA37" t="n">
         <v>24</v>
       </c>
     </row>
@@ -10225,27 +9963,29 @@
         <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
         <v>14</v>
       </c>
-      <c r="R38" t="n">
-        <v>6</v>
-      </c>
       <c r="S38" t="n">
-        <v>14</v>
-      </c>
-      <c r="T38" t="n">
         <v>0</v>
       </c>
-      <c r="U38" t="inlineStr">
+      <c r="T38" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="V38" t="n">
-        <v>10</v>
+      <c r="U38" t="n">
+        <v>5</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
@@ -10254,18 +9994,13 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
           <t>Stahlkappe + Schienen</t>
         </is>
       </c>
+      <c r="Y38" t="n">
+        <v>100</v>
+      </c>
       <c r="Z38" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA38" t="n">
         <v>60</v>
       </c>
     </row>
@@ -10336,27 +10071,29 @@
         <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q39" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" t="n">
         <v>19</v>
       </c>
-      <c r="R39" t="n">
-        <v>8</v>
-      </c>
       <c r="S39" t="n">
-        <v>19</v>
-      </c>
-      <c r="T39" t="n">
         <v>0</v>
       </c>
-      <c r="U39" t="inlineStr">
+      <c r="T39" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="V39" t="n">
-        <v>14</v>
+      <c r="U39" t="n">
+        <v>7</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
@@ -10365,18 +10102,13 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
           <t>Stahlkappe + Schienen</t>
         </is>
       </c>
+      <c r="Y39" t="n">
+        <v>200</v>
+      </c>
       <c r="Z39" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA39" t="n">
         <v>120</v>
       </c>
     </row>
@@ -10447,27 +10179,29 @@
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
-      </c>
-      <c r="T40" t="n">
         <v>0</v>
       </c>
-      <c r="U40" t="inlineStr">
+      <c r="T40" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="V40" t="n">
-        <v>18</v>
+      <c r="U40" t="n">
+        <v>9</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
@@ -10476,18 +10210,13 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
           <t>Stahlkappe + Schienen</t>
         </is>
       </c>
+      <c r="Y40" t="n">
+        <v>500</v>
+      </c>
       <c r="Z40" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA40" t="n">
         <v>300</v>
       </c>
     </row>
@@ -10558,27 +10287,29 @@
         <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
-      <c r="T41" t="n">
-        <v>0</v>
-      </c>
-      <c r="U41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="V41" t="n">
-        <v>0</v>
+      <c r="U41" t="n">
+        <v>12</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
@@ -10587,15 +10318,10 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
           <t>Stahlkappe + Schienen</t>
         </is>
       </c>
-      <c r="AA41" t="n">
+      <c r="Z41" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -10630,7 +10356,6 @@
       <c r="X42" s="3" t="n"/>
       <c r="Y42" s="3" t="n"/>
       <c r="Z42" s="3" t="n"/>
-      <c r="AA42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -10710,16 +10435,18 @@
       <c r="S43" t="n">
         <v>0</v>
       </c>
-      <c r="T43" t="n">
-        <v>0</v>
-      </c>
-      <c r="U43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V43" t="n">
-        <v>3</v>
+      <c r="U43" t="n">
+        <v>2</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
@@ -10728,18 +10455,13 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
           <t>Metallzacken + Riemen</t>
         </is>
       </c>
+      <c r="Y43" t="n">
+        <v>10</v>
+      </c>
       <c r="Z43" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA43" t="n">
         <v>6</v>
       </c>
     </row>
@@ -10821,16 +10543,18 @@
       <c r="S44" t="n">
         <v>0</v>
       </c>
-      <c r="T44" t="n">
-        <v>0</v>
-      </c>
-      <c r="U44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V44" t="n">
-        <v>5</v>
+      <c r="U44" t="n">
+        <v>3</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
@@ -10839,18 +10563,13 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
           <t>Metallzacken + Riemen</t>
         </is>
       </c>
+      <c r="Y44" t="n">
+        <v>20</v>
+      </c>
       <c r="Z44" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA44" t="n">
         <v>12</v>
       </c>
     </row>
@@ -10932,16 +10651,18 @@
       <c r="S45" t="n">
         <v>0</v>
       </c>
-      <c r="T45" t="n">
-        <v>0</v>
-      </c>
-      <c r="U45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V45" t="n">
-        <v>7</v>
+      <c r="U45" t="n">
+        <v>4</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
@@ -10950,18 +10671,13 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
           <t>Metallzacken + Riemen</t>
         </is>
       </c>
+      <c r="Y45" t="n">
+        <v>40</v>
+      </c>
       <c r="Z45" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA45" t="n">
         <v>24</v>
       </c>
     </row>
@@ -11043,16 +10759,18 @@
       <c r="S46" t="n">
         <v>0</v>
       </c>
-      <c r="T46" t="n">
-        <v>0</v>
-      </c>
-      <c r="U46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V46" t="n">
-        <v>10</v>
+      <c r="U46" t="n">
+        <v>5</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
@@ -11061,18 +10779,13 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
           <t>Metallzacken + Riemen</t>
         </is>
       </c>
+      <c r="Y46" t="n">
+        <v>100</v>
+      </c>
       <c r="Z46" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA46" t="n">
         <v>60</v>
       </c>
     </row>
@@ -11154,16 +10867,18 @@
       <c r="S47" t="n">
         <v>0</v>
       </c>
-      <c r="T47" t="n">
-        <v>0</v>
-      </c>
-      <c r="U47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V47" t="n">
-        <v>14</v>
+      <c r="U47" t="n">
+        <v>7</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W47" t="inlineStr">
         <is>
@@ -11172,18 +10887,13 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
           <t>Metallzacken + Riemen</t>
         </is>
       </c>
+      <c r="Y47" t="n">
+        <v>200</v>
+      </c>
       <c r="Z47" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA47" t="n">
         <v>120</v>
       </c>
     </row>
@@ -11265,16 +10975,18 @@
       <c r="S48" t="n">
         <v>0</v>
       </c>
-      <c r="T48" t="n">
-        <v>0</v>
-      </c>
-      <c r="U48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V48" t="n">
-        <v>18</v>
+      <c r="U48" t="n">
+        <v>9</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
@@ -11283,18 +10995,13 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
           <t>Metallzacken + Riemen</t>
         </is>
       </c>
+      <c r="Y48" t="n">
+        <v>500</v>
+      </c>
       <c r="Z48" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA48" t="n">
         <v>300</v>
       </c>
     </row>
@@ -11376,16 +11083,18 @@
       <c r="S49" t="n">
         <v>0</v>
       </c>
-      <c r="T49" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V49" t="n">
-        <v>0</v>
+      <c r="U49" t="n">
+        <v>12</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
@@ -11394,15 +11103,10 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
           <t>Metallzacken + Riemen</t>
         </is>
       </c>
-      <c r="AA49" t="n">
+      <c r="Z49" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -11437,7 +11141,6 @@
       <c r="X50" s="3" t="n"/>
       <c r="Y50" s="3" t="n"/>
       <c r="Z50" s="3" t="n"/>
-      <c r="AA50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -11517,16 +11220,18 @@
       <c r="S51" t="n">
         <v>0</v>
       </c>
-      <c r="T51" t="n">
-        <v>0</v>
-      </c>
-      <c r="U51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V51" t="n">
-        <v>3</v>
+      <c r="U51" t="n">
+        <v>2</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
@@ -11535,18 +11240,13 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
           <t>Verzauberte Sohle + Feder</t>
         </is>
       </c>
+      <c r="Y51" t="n">
+        <v>10</v>
+      </c>
       <c r="Z51" t="n">
-        <v>10</v>
-      </c>
-      <c r="AA51" t="n">
         <v>6</v>
       </c>
     </row>
@@ -11628,16 +11328,18 @@
       <c r="S52" t="n">
         <v>0</v>
       </c>
-      <c r="T52" t="n">
-        <v>0</v>
-      </c>
-      <c r="U52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V52" t="n">
-        <v>5</v>
+      <c r="U52" t="n">
+        <v>3</v>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
@@ -11646,18 +11348,13 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
           <t>Verzauberte Sohle + Feder</t>
         </is>
       </c>
+      <c r="Y52" t="n">
+        <v>20</v>
+      </c>
       <c r="Z52" t="n">
-        <v>20</v>
-      </c>
-      <c r="AA52" t="n">
         <v>12</v>
       </c>
     </row>
@@ -11739,16 +11436,18 @@
       <c r="S53" t="n">
         <v>0</v>
       </c>
-      <c r="T53" t="n">
-        <v>0</v>
-      </c>
-      <c r="U53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V53" t="n">
-        <v>7</v>
+      <c r="U53" t="n">
+        <v>4</v>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
@@ -11757,18 +11456,13 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
           <t>Verzauberte Sohle + Feder</t>
         </is>
       </c>
+      <c r="Y53" t="n">
+        <v>40</v>
+      </c>
       <c r="Z53" t="n">
-        <v>40</v>
-      </c>
-      <c r="AA53" t="n">
         <v>24</v>
       </c>
     </row>
@@ -11850,16 +11544,18 @@
       <c r="S54" t="n">
         <v>0</v>
       </c>
-      <c r="T54" t="n">
-        <v>0</v>
-      </c>
-      <c r="U54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V54" t="n">
-        <v>10</v>
+      <c r="U54" t="n">
+        <v>5</v>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
@@ -11868,18 +11564,13 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
           <t>Verzauberte Sohle + Feder</t>
         </is>
       </c>
+      <c r="Y54" t="n">
+        <v>100</v>
+      </c>
       <c r="Z54" t="n">
-        <v>100</v>
-      </c>
-      <c r="AA54" t="n">
         <v>60</v>
       </c>
     </row>
@@ -11961,16 +11652,18 @@
       <c r="S55" t="n">
         <v>0</v>
       </c>
-      <c r="T55" t="n">
-        <v>0</v>
-      </c>
-      <c r="U55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V55" t="n">
-        <v>14</v>
+      <c r="U55" t="n">
+        <v>7</v>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
@@ -11979,18 +11672,13 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
           <t>Verzauberte Sohle + Feder</t>
         </is>
       </c>
+      <c r="Y55" t="n">
+        <v>200</v>
+      </c>
       <c r="Z55" t="n">
-        <v>200</v>
-      </c>
-      <c r="AA55" t="n">
         <v>120</v>
       </c>
     </row>
@@ -12072,16 +11760,18 @@
       <c r="S56" t="n">
         <v>0</v>
       </c>
-      <c r="T56" t="n">
-        <v>0</v>
-      </c>
-      <c r="U56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V56" t="n">
-        <v>18</v>
+      <c r="U56" t="n">
+        <v>9</v>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
@@ -12090,18 +11780,13 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
           <t>Verzauberte Sohle + Feder</t>
         </is>
       </c>
+      <c r="Y56" t="n">
+        <v>500</v>
+      </c>
       <c r="Z56" t="n">
-        <v>500</v>
-      </c>
-      <c r="AA56" t="n">
         <v>300</v>
       </c>
     </row>
@@ -12183,16 +11868,18 @@
       <c r="S57" t="n">
         <v>0</v>
       </c>
-      <c r="T57" t="n">
-        <v>0</v>
-      </c>
-      <c r="U57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="V57" t="n">
-        <v>0</v>
+      <c r="U57" t="n">
+        <v>12</v>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
@@ -12201,15 +11888,10 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="Y57" t="inlineStr">
-        <is>
           <t>Verzauberte Sohle + Feder</t>
         </is>
       </c>
-      <c r="AA57" t="n">
+      <c r="Z57" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -39894,7 +39576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z57"/>
+  <dimension ref="A1:Y57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -40003,55 +39685,50 @@
       </c>
       <c r="P1" s="4" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>Rüstung (phys. flach)</t>
         </is>
       </c>
       <c r="Q1" s="4" t="inlineStr">
         <is>
-          <t>Rüstung (phys. flach)</t>
+          <t>Resistenz (mag. flach)</t>
         </is>
       </c>
       <c r="R1" s="4" t="inlineStr">
         <is>
-          <t>Resistenz (mag. flach)</t>
+          <t>VIT/LP-Bonus</t>
         </is>
       </c>
       <c r="S1" s="4" t="inlineStr">
         <is>
-          <t>VIT/LP-Bonus</t>
+          <t>Prim. Attr.</t>
         </is>
       </c>
       <c r="T1" s="4" t="inlineStr">
         <is>
-          <t>Prim. Attr.</t>
+          <t>Prim. Wert</t>
         </is>
       </c>
       <c r="U1" s="4" t="inlineStr">
         <is>
-          <t>Prim. Wert</t>
+          <t>Sek. Attr.</t>
         </is>
       </c>
       <c r="V1" s="4" t="inlineStr">
         <is>
-          <t>Sek. Attr.</t>
+          <t>Sek. Wert</t>
         </is>
       </c>
       <c r="W1" s="4" t="inlineStr">
         <is>
-          <t>Sek. Wert</t>
+          <t>Bauteile</t>
         </is>
       </c>
       <c r="X1" s="4" t="inlineStr">
         <is>
-          <t>Bauteile</t>
+          <t>Kaufpreis (Barren)</t>
         </is>
       </c>
       <c r="Y1" s="4" t="inlineStr">
-        <is>
-          <t>Kaufpreis (Barren)</t>
-        </is>
-      </c>
-      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>Verkaufspreis</t>
         </is>
@@ -40087,7 +39764,6 @@
       <c r="W2" s="3" t="n"/>
       <c r="X2" s="3" t="n"/>
       <c r="Y2" s="3" t="n"/>
-      <c r="Z2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -40156,24 +39832,26 @@
         <v>1</v>
       </c>
       <c r="P3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
-        <v>3</v>
-      </c>
-      <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U3" t="n">
-        <v>3</v>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -40182,18 +39860,13 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
           <t>Stoffkapuze + Kordel</t>
         </is>
       </c>
+      <c r="X3" t="n">
+        <v>10</v>
+      </c>
       <c r="Y3" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -40264,24 +39937,26 @@
         <v>2</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>6</v>
-      </c>
-      <c r="S4" t="n">
         <v>4</v>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U4" t="n">
-        <v>5</v>
+      <c r="T4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -40290,18 +39965,13 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
           <t>Stoffkapuze + Kordel</t>
         </is>
       </c>
+      <c r="X4" t="n">
+        <v>20</v>
+      </c>
       <c r="Y4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z4" t="n">
         <v>12</v>
       </c>
     </row>
@@ -40372,24 +40042,26 @@
         <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R5" t="n">
-        <v>10</v>
-      </c>
-      <c r="S5" t="n">
         <v>5</v>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U5" t="n">
-        <v>7</v>
+      <c r="T5" t="n">
+        <v>4</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -40398,18 +40070,13 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
           <t>Stoffkapuze + Kordel</t>
         </is>
       </c>
+      <c r="X5" t="n">
+        <v>40</v>
+      </c>
       <c r="Y5" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z5" t="n">
         <v>24</v>
       </c>
     </row>
@@ -40480,24 +40147,26 @@
         <v>3</v>
       </c>
       <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
         <v>5</v>
       </c>
-      <c r="Q6" t="n">
-        <v>2</v>
-      </c>
       <c r="R6" t="n">
-        <v>13</v>
-      </c>
-      <c r="S6" t="n">
         <v>7</v>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U6" t="n">
-        <v>10</v>
+      <c r="T6" t="n">
+        <v>5</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -40506,18 +40175,13 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
           <t>Stoffkapuze + Kordel</t>
         </is>
       </c>
+      <c r="X6" t="n">
+        <v>100</v>
+      </c>
       <c r="Y6" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z6" t="n">
         <v>60</v>
       </c>
     </row>
@@ -40588,24 +40252,26 @@
         <v>3</v>
       </c>
       <c r="P7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="Q7" t="n">
-        <v>2</v>
-      </c>
       <c r="R7" t="n">
-        <v>18</v>
-      </c>
-      <c r="S7" t="n">
         <v>10</v>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U7" t="n">
-        <v>14</v>
+      <c r="T7" t="n">
+        <v>7</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -40614,18 +40280,13 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
           <t>Stoffkapuze + Kordel</t>
         </is>
       </c>
+      <c r="X7" t="n">
+        <v>200</v>
+      </c>
       <c r="Y7" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z7" t="n">
         <v>120</v>
       </c>
     </row>
@@ -40696,24 +40357,26 @@
         <v>3</v>
       </c>
       <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
         <v>8</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3</v>
-      </c>
       <c r="R8" t="n">
-        <v>24</v>
-      </c>
-      <c r="S8" t="n">
         <v>13</v>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U8" t="n">
-        <v>18</v>
+      <c r="T8" t="n">
+        <v>9</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -40722,18 +40385,13 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
           <t>Stoffkapuze + Kordel</t>
         </is>
       </c>
+      <c r="X8" t="n">
+        <v>500</v>
+      </c>
       <c r="Y8" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z8" t="n">
         <v>300</v>
       </c>
     </row>
@@ -40804,24 +40462,26 @@
         <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" t="inlineStr">
+        <v>17</v>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>WIL</t>
         </is>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
+      <c r="T9" t="n">
+        <v>12</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -40830,15 +40490,10 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
           <t>Stoffkapuze + Kordel</t>
         </is>
       </c>
-      <c r="Z9" t="n">
+      <c r="Y9" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -40872,7 +40527,6 @@
       <c r="W10" s="3" t="n"/>
       <c r="X10" s="3" t="n"/>
       <c r="Y10" s="3" t="n"/>
-      <c r="Z10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -40941,24 +40595,26 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>3</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>GES</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
         <v>2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>2</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>GES</t>
-        </is>
-      </c>
-      <c r="U11" t="n">
-        <v>3</v>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -40967,18 +40623,13 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
           <t>Lederkappe + Riemen</t>
         </is>
       </c>
+      <c r="X11" t="n">
+        <v>10</v>
+      </c>
       <c r="Y11" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z11" t="n">
         <v>6</v>
       </c>
     </row>
@@ -41052,21 +40703,23 @@
         <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>3</v>
-      </c>
-      <c r="S12" t="n">
         <v>5</v>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U12" t="n">
-        <v>5</v>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -41075,18 +40728,13 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
           <t>Lederkappe + Riemen</t>
         </is>
       </c>
+      <c r="X12" t="n">
+        <v>20</v>
+      </c>
       <c r="Y12" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z12" t="n">
         <v>12</v>
       </c>
     </row>
@@ -41157,24 +40805,26 @@
         <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q13" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="R13" t="n">
-        <v>5</v>
-      </c>
-      <c r="S13" t="n">
         <v>6</v>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U13" t="n">
-        <v>7</v>
+      <c r="T13" t="n">
+        <v>4</v>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -41183,18 +40833,13 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
           <t>Lederkappe + Riemen</t>
         </is>
       </c>
+      <c r="X13" t="n">
+        <v>40</v>
+      </c>
       <c r="Y13" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z13" t="n">
         <v>24</v>
       </c>
     </row>
@@ -41265,24 +40910,26 @@
         <v>3</v>
       </c>
       <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>2</v>
+      </c>
+      <c r="R14" t="n">
+        <v>10</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>GES</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
         <v>5</v>
       </c>
-      <c r="Q14" t="n">
-        <v>6</v>
-      </c>
-      <c r="R14" t="n">
-        <v>6</v>
-      </c>
-      <c r="S14" t="n">
-        <v>10</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>GES</t>
-        </is>
-      </c>
-      <c r="U14" t="n">
-        <v>10</v>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -41291,18 +40938,13 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
           <t>Lederkappe + Riemen</t>
         </is>
       </c>
+      <c r="X14" t="n">
+        <v>100</v>
+      </c>
       <c r="Y14" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z14" t="n">
         <v>60</v>
       </c>
     </row>
@@ -41373,24 +41015,26 @@
         <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q15" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>9</v>
-      </c>
-      <c r="S15" t="n">
         <v>13</v>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U15" t="n">
-        <v>14</v>
+      <c r="T15" t="n">
+        <v>7</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -41399,18 +41043,13 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
           <t>Lederkappe + Riemen</t>
         </is>
       </c>
+      <c r="X15" t="n">
+        <v>200</v>
+      </c>
       <c r="Y15" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z15" t="n">
         <v>120</v>
       </c>
     </row>
@@ -41481,24 +41120,26 @@
         <v>3</v>
       </c>
       <c r="P16" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q16" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="R16" t="n">
-        <v>12</v>
-      </c>
-      <c r="S16" t="n">
         <v>17</v>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U16" t="n">
-        <v>18</v>
+      <c r="T16" t="n">
+        <v>9</v>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -41507,18 +41148,13 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
           <t>Lederkappe + Riemen</t>
         </is>
       </c>
+      <c r="X16" t="n">
+        <v>500</v>
+      </c>
       <c r="Y16" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z16" t="n">
         <v>300</v>
       </c>
     </row>
@@ -41589,24 +41225,26 @@
         <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="inlineStr">
+        <v>22</v>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
+      <c r="T17" t="n">
+        <v>12</v>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -41615,15 +41253,10 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
           <t>Lederkappe + Riemen</t>
         </is>
       </c>
-      <c r="Z17" t="n">
+      <c r="Y17" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -41657,7 +41290,6 @@
       <c r="W18" s="3" t="n"/>
       <c r="X18" s="3" t="n"/>
       <c r="Y18" s="3" t="n"/>
-      <c r="Z18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -41726,24 +41358,26 @@
         <v>1</v>
       </c>
       <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>4</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="Q19" t="n">
-        <v>2</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2</v>
-      </c>
-      <c r="S19" t="n">
-        <v>4</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>VIT</t>
-        </is>
-      </c>
-      <c r="U19" t="n">
-        <v>3</v>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -41752,18 +41386,13 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Polster</t>
         </is>
       </c>
+      <c r="X19" t="n">
+        <v>10</v>
+      </c>
       <c r="Y19" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z19" t="n">
         <v>6</v>
       </c>
     </row>
@@ -41834,24 +41463,26 @@
         <v>2</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="R20" t="n">
-        <v>4</v>
-      </c>
-      <c r="S20" t="n">
         <v>6</v>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="U20" t="n">
-        <v>5</v>
+      <c r="T20" t="n">
+        <v>3</v>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -41860,18 +41491,13 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Polster</t>
         </is>
       </c>
+      <c r="X20" t="n">
+        <v>20</v>
+      </c>
       <c r="Y20" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z20" t="n">
         <v>12</v>
       </c>
     </row>
@@ -41942,24 +41568,26 @@
         <v>3</v>
       </c>
       <c r="P21" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2</v>
+      </c>
+      <c r="R21" t="n">
+        <v>8</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>VIT</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
         <v>4</v>
       </c>
-      <c r="Q21" t="n">
-        <v>6</v>
-      </c>
-      <c r="R21" t="n">
-        <v>6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>8</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>VIT</t>
-        </is>
-      </c>
-      <c r="U21" t="n">
-        <v>7</v>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -41968,18 +41596,13 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Polster</t>
         </is>
       </c>
+      <c r="X21" t="n">
+        <v>40</v>
+      </c>
       <c r="Y21" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z21" t="n">
         <v>24</v>
       </c>
     </row>
@@ -42050,24 +41673,26 @@
         <v>3</v>
       </c>
       <c r="P22" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>8</v>
-      </c>
-      <c r="S22" t="n">
         <v>12</v>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="U22" t="n">
-        <v>10</v>
+      <c r="T22" t="n">
+        <v>5</v>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -42076,18 +41701,13 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Polster</t>
         </is>
       </c>
+      <c r="X22" t="n">
+        <v>100</v>
+      </c>
       <c r="Y22" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z22" t="n">
         <v>60</v>
       </c>
     </row>
@@ -42158,24 +41778,26 @@
         <v>3</v>
       </c>
       <c r="P23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="R23" t="n">
-        <v>11</v>
-      </c>
-      <c r="S23" t="n">
         <v>16</v>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="U23" t="n">
-        <v>14</v>
+      <c r="T23" t="n">
+        <v>7</v>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -42184,18 +41806,13 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Polster</t>
         </is>
       </c>
+      <c r="X23" t="n">
+        <v>200</v>
+      </c>
       <c r="Y23" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z23" t="n">
         <v>120</v>
       </c>
     </row>
@@ -42266,24 +41883,26 @@
         <v>3</v>
       </c>
       <c r="P24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="R24" t="n">
-        <v>15</v>
-      </c>
-      <c r="S24" t="n">
         <v>21</v>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="U24" t="n">
-        <v>18</v>
+      <c r="T24" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -42292,18 +41911,13 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Polster</t>
         </is>
       </c>
+      <c r="X24" t="n">
+        <v>500</v>
+      </c>
       <c r="Y24" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z24" t="n">
         <v>300</v>
       </c>
     </row>
@@ -42374,24 +41988,26 @@
         <v>3</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="n">
-        <v>0</v>
-      </c>
-      <c r="T25" t="inlineStr">
+        <v>28</v>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>VIT</t>
         </is>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
+      <c r="T25" t="n">
+        <v>12</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -42400,15 +42016,10 @@
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
           <t>Kettengeflecht + Polster</t>
         </is>
       </c>
-      <c r="Z25" t="n">
+      <c r="Y25" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -42442,7 +42053,6 @@
       <c r="W26" s="3" t="n"/>
       <c r="X26" s="3" t="n"/>
       <c r="Y26" s="3" t="n"/>
-      <c r="Z26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -42511,24 +42121,26 @@
         <v>1</v>
       </c>
       <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>4</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T27" t="n">
         <v>2</v>
       </c>
-      <c r="Q27" t="n">
-        <v>3</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U27" t="n">
-        <v>3</v>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -42537,18 +42149,13 @@
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
           <t>Schuppen + Helmglocke</t>
         </is>
       </c>
+      <c r="X27" t="n">
+        <v>10</v>
+      </c>
       <c r="Y27" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z27" t="n">
         <v>6</v>
       </c>
     </row>
@@ -42622,21 +42229,23 @@
         <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R28" t="n">
-        <v>2</v>
-      </c>
-      <c r="S28" t="n">
         <v>7</v>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="U28" t="n">
-        <v>5</v>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -42645,18 +42254,13 @@
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
           <t>Schuppen + Helmglocke</t>
         </is>
       </c>
+      <c r="X28" t="n">
+        <v>20</v>
+      </c>
       <c r="Y28" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z28" t="n">
         <v>12</v>
       </c>
     </row>
@@ -42727,24 +42331,26 @@
         <v>3</v>
       </c>
       <c r="P29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>1</v>
+      </c>
+      <c r="R29" t="n">
+        <v>9</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T29" t="n">
         <v>4</v>
       </c>
-      <c r="Q29" t="n">
-        <v>8</v>
-      </c>
-      <c r="R29" t="n">
-        <v>4</v>
-      </c>
-      <c r="S29" t="n">
-        <v>9</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U29" t="n">
-        <v>7</v>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -42753,18 +42359,13 @@
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
           <t>Schuppen + Helmglocke</t>
         </is>
       </c>
+      <c r="X29" t="n">
+        <v>40</v>
+      </c>
       <c r="Y29" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z29" t="n">
         <v>24</v>
       </c>
     </row>
@@ -42835,24 +42436,26 @@
         <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="R30" t="n">
+        <v>13</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T30" t="n">
         <v>5</v>
       </c>
-      <c r="S30" t="n">
-        <v>13</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U30" t="n">
-        <v>10</v>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -42861,18 +42464,13 @@
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
           <t>Schuppen + Helmglocke</t>
         </is>
       </c>
+      <c r="X30" t="n">
+        <v>100</v>
+      </c>
       <c r="Y30" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z30" t="n">
         <v>60</v>
       </c>
     </row>
@@ -42943,24 +42541,26 @@
         <v>3</v>
       </c>
       <c r="P31" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q31" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="R31" t="n">
+        <v>18</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T31" t="n">
         <v>7</v>
       </c>
-      <c r="S31" t="n">
-        <v>18</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U31" t="n">
-        <v>14</v>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -42969,18 +42569,13 @@
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
           <t>Schuppen + Helmglocke</t>
         </is>
       </c>
+      <c r="X31" t="n">
+        <v>200</v>
+      </c>
       <c r="Y31" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z31" t="n">
         <v>120</v>
       </c>
     </row>
@@ -43051,24 +42646,26 @@
         <v>3</v>
       </c>
       <c r="P32" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Q32" t="n">
-        <v>21</v>
+        <v>3</v>
       </c>
       <c r="R32" t="n">
+        <v>23</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="T32" t="n">
         <v>9</v>
       </c>
-      <c r="S32" t="n">
-        <v>23</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="U32" t="n">
-        <v>18</v>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -43077,18 +42674,13 @@
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
           <t>Schuppen + Helmglocke</t>
         </is>
       </c>
+      <c r="X32" t="n">
+        <v>500</v>
+      </c>
       <c r="Y32" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z32" t="n">
         <v>300</v>
       </c>
     </row>
@@ -43159,24 +42751,26 @@
         <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="inlineStr">
+        <v>31</v>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="U33" t="n">
-        <v>0</v>
+      <c r="T33" t="n">
+        <v>12</v>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -43185,15 +42779,10 @@
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
           <t>Schuppen + Helmglocke</t>
         </is>
       </c>
-      <c r="Z33" t="n">
+      <c r="Y33" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -43227,7 +42816,6 @@
       <c r="W34" s="3" t="n"/>
       <c r="X34" s="3" t="n"/>
       <c r="Y34" s="3" t="n"/>
-      <c r="Z34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -43296,24 +42884,26 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="R35" t="n">
-        <v>1</v>
-      </c>
-      <c r="S35" t="n">
         <v>5</v>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="U35" t="n">
-        <v>3</v>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -43322,18 +42912,13 @@
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
           <t>Helmglocke + Visier</t>
         </is>
       </c>
+      <c r="X35" t="n">
+        <v>10</v>
+      </c>
       <c r="Y35" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z35" t="n">
         <v>6</v>
       </c>
     </row>
@@ -43404,24 +42989,26 @@
         <v>2</v>
       </c>
       <c r="P36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q36" t="n">
+        <v>1</v>
+      </c>
+      <c r="R36" t="n">
         <v>7</v>
       </c>
-      <c r="R36" t="n">
-        <v>3</v>
-      </c>
-      <c r="S36" t="n">
-        <v>7</v>
-      </c>
-      <c r="T36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="U36" t="n">
-        <v>5</v>
+      <c r="T36" t="n">
+        <v>3</v>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -43430,18 +43017,13 @@
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
           <t>Helmglocke + Visier</t>
         </is>
       </c>
+      <c r="X36" t="n">
+        <v>20</v>
+      </c>
       <c r="Y36" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z36" t="n">
         <v>12</v>
       </c>
     </row>
@@ -43512,24 +43094,26 @@
         <v>3</v>
       </c>
       <c r="P37" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="n">
+        <v>1</v>
+      </c>
+      <c r="R37" t="n">
         <v>10</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="T37" t="n">
         <v>4</v>
       </c>
-      <c r="S37" t="n">
-        <v>10</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
-      <c r="U37" t="n">
-        <v>7</v>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -43538,18 +43122,13 @@
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
           <t>Helmglocke + Visier</t>
         </is>
       </c>
+      <c r="X37" t="n">
+        <v>40</v>
+      </c>
       <c r="Y37" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z37" t="n">
         <v>24</v>
       </c>
     </row>
@@ -43620,24 +43199,26 @@
         <v>3</v>
       </c>
       <c r="P38" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q38" t="n">
+        <v>2</v>
+      </c>
+      <c r="R38" t="n">
         <v>14</v>
       </c>
-      <c r="R38" t="n">
-        <v>6</v>
-      </c>
-      <c r="S38" t="n">
-        <v>14</v>
-      </c>
-      <c r="T38" t="inlineStr">
+      <c r="S38" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="U38" t="n">
-        <v>10</v>
+      <c r="T38" t="n">
+        <v>5</v>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -43646,18 +43227,13 @@
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
           <t>Helmglocke + Visier</t>
         </is>
       </c>
+      <c r="X38" t="n">
+        <v>100</v>
+      </c>
       <c r="Y38" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z38" t="n">
         <v>60</v>
       </c>
     </row>
@@ -43728,24 +43304,26 @@
         <v>3</v>
       </c>
       <c r="P39" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="Q39" t="n">
+        <v>3</v>
+      </c>
+      <c r="R39" t="n">
         <v>19</v>
       </c>
-      <c r="R39" t="n">
-        <v>8</v>
-      </c>
-      <c r="S39" t="n">
-        <v>19</v>
-      </c>
-      <c r="T39" t="inlineStr">
+      <c r="S39" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="U39" t="n">
-        <v>14</v>
+      <c r="T39" t="n">
+        <v>7</v>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -43754,18 +43332,13 @@
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
           <t>Helmglocke + Visier</t>
         </is>
       </c>
+      <c r="X39" t="n">
+        <v>200</v>
+      </c>
       <c r="Y39" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z39" t="n">
         <v>120</v>
       </c>
     </row>
@@ -43836,24 +43409,26 @@
         <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="Q40" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="R40" t="n">
-        <v>10</v>
-      </c>
-      <c r="S40" t="n">
         <v>25</v>
       </c>
-      <c r="T40" t="inlineStr">
+      <c r="S40" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="U40" t="n">
-        <v>18</v>
+      <c r="T40" t="n">
+        <v>9</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -43862,18 +43437,13 @@
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
           <t>Helmglocke + Visier</t>
         </is>
       </c>
+      <c r="X40" t="n">
+        <v>500</v>
+      </c>
       <c r="Y40" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z40" t="n">
         <v>300</v>
       </c>
     </row>
@@ -43944,24 +43514,26 @@
         <v>3</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0</v>
-      </c>
-      <c r="T41" t="inlineStr">
+        <v>34</v>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="U41" t="n">
-        <v>0</v>
+      <c r="T41" t="n">
+        <v>12</v>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -43970,15 +43542,10 @@
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
           <t>Helmglocke + Visier</t>
         </is>
       </c>
-      <c r="Z41" t="n">
+      <c r="Y41" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -44012,7 +43579,6 @@
       <c r="W42" s="3" t="n"/>
       <c r="X42" s="3" t="n"/>
       <c r="Y42" s="3" t="n"/>
-      <c r="Z42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -44089,16 +43655,18 @@
       <c r="R43" t="n">
         <v>0</v>
       </c>
-      <c r="S43" t="n">
-        <v>0</v>
-      </c>
-      <c r="T43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U43" t="n">
-        <v>3</v>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -44107,18 +43675,13 @@
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
           <t>Metallvisier + Schliffglas</t>
         </is>
       </c>
+      <c r="X43" t="n">
+        <v>10</v>
+      </c>
       <c r="Y43" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z43" t="n">
         <v>6</v>
       </c>
     </row>
@@ -44197,16 +43760,18 @@
       <c r="R44" t="n">
         <v>0</v>
       </c>
-      <c r="S44" t="n">
-        <v>0</v>
-      </c>
-      <c r="T44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U44" t="n">
-        <v>5</v>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -44215,18 +43780,13 @@
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
           <t>Metallvisier + Schliffglas</t>
         </is>
       </c>
+      <c r="X44" t="n">
+        <v>20</v>
+      </c>
       <c r="Y44" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z44" t="n">
         <v>12</v>
       </c>
     </row>
@@ -44305,16 +43865,18 @@
       <c r="R45" t="n">
         <v>0</v>
       </c>
-      <c r="S45" t="n">
-        <v>0</v>
-      </c>
-      <c r="T45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U45" t="n">
-        <v>7</v>
+      <c r="T45" t="n">
+        <v>4</v>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -44323,18 +43885,13 @@
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
           <t>Metallvisier + Schliffglas</t>
         </is>
       </c>
+      <c r="X45" t="n">
+        <v>40</v>
+      </c>
       <c r="Y45" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z45" t="n">
         <v>24</v>
       </c>
     </row>
@@ -44413,16 +43970,18 @@
       <c r="R46" t="n">
         <v>0</v>
       </c>
-      <c r="S46" t="n">
-        <v>0</v>
-      </c>
-      <c r="T46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U46" t="n">
-        <v>10</v>
+      <c r="T46" t="n">
+        <v>5</v>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -44431,18 +43990,13 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
           <t>Metallvisier + Schliffglas</t>
         </is>
       </c>
+      <c r="X46" t="n">
+        <v>100</v>
+      </c>
       <c r="Y46" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z46" t="n">
         <v>60</v>
       </c>
     </row>
@@ -44521,16 +44075,18 @@
       <c r="R47" t="n">
         <v>0</v>
       </c>
-      <c r="S47" t="n">
-        <v>0</v>
-      </c>
-      <c r="T47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U47" t="n">
-        <v>14</v>
+      <c r="T47" t="n">
+        <v>7</v>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -44539,18 +44095,13 @@
       </c>
       <c r="W47" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
           <t>Metallvisier + Schliffglas</t>
         </is>
       </c>
+      <c r="X47" t="n">
+        <v>200</v>
+      </c>
       <c r="Y47" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z47" t="n">
         <v>120</v>
       </c>
     </row>
@@ -44629,16 +44180,18 @@
       <c r="R48" t="n">
         <v>0</v>
       </c>
-      <c r="S48" t="n">
-        <v>0</v>
-      </c>
-      <c r="T48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U48" t="n">
-        <v>18</v>
+      <c r="T48" t="n">
+        <v>9</v>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -44647,18 +44200,13 @@
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
           <t>Metallvisier + Schliffglas</t>
         </is>
       </c>
+      <c r="X48" t="n">
+        <v>500</v>
+      </c>
       <c r="Y48" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z48" t="n">
         <v>300</v>
       </c>
     </row>
@@ -44737,16 +44285,18 @@
       <c r="R49" t="n">
         <v>0</v>
       </c>
-      <c r="S49" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>GES</t>
         </is>
       </c>
-      <c r="U49" t="n">
-        <v>0</v>
+      <c r="T49" t="n">
+        <v>12</v>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -44755,15 +44305,10 @@
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
           <t>Metallvisier + Schliffglas</t>
         </is>
       </c>
-      <c r="Z49" t="n">
+      <c r="Y49" t="n">
         <v>1000</v>
       </c>
     </row>
@@ -44797,7 +44342,6 @@
       <c r="W50" s="3" t="n"/>
       <c r="X50" s="3" t="n"/>
       <c r="Y50" s="3" t="n"/>
-      <c r="Z50" s="3" t="n"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -44874,16 +44418,18 @@
       <c r="R51" t="n">
         <v>0</v>
       </c>
-      <c r="S51" t="n">
-        <v>0</v>
-      </c>
-      <c r="T51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="U51" t="n">
-        <v>3</v>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -44892,18 +44438,13 @@
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
           <t>Reif + Fassung</t>
         </is>
       </c>
+      <c r="X51" t="n">
+        <v>10</v>
+      </c>
       <c r="Y51" t="n">
-        <v>10</v>
-      </c>
-      <c r="Z51" t="n">
         <v>6</v>
       </c>
     </row>
@@ -44982,16 +44523,18 @@
       <c r="R52" t="n">
         <v>0</v>
       </c>
-      <c r="S52" t="n">
-        <v>0</v>
-      </c>
-      <c r="T52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="U52" t="n">
-        <v>5</v>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -45000,18 +44543,13 @@
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
           <t>Reif + Fassung</t>
         </is>
       </c>
+      <c r="X52" t="n">
+        <v>20</v>
+      </c>
       <c r="Y52" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z52" t="n">
         <v>12</v>
       </c>
     </row>
@@ -45090,16 +44628,18 @@
       <c r="R53" t="n">
         <v>0</v>
       </c>
-      <c r="S53" t="n">
-        <v>0</v>
-      </c>
-      <c r="T53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="U53" t="n">
-        <v>7</v>
+      <c r="T53" t="n">
+        <v>4</v>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -45108,18 +44648,13 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
           <t>Reif + Fassung</t>
         </is>
       </c>
+      <c r="X53" t="n">
+        <v>40</v>
+      </c>
       <c r="Y53" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z53" t="n">
         <v>24</v>
       </c>
     </row>
@@ -45198,16 +44733,18 @@
       <c r="R54" t="n">
         <v>0</v>
       </c>
-      <c r="S54" t="n">
-        <v>0</v>
-      </c>
-      <c r="T54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="U54" t="n">
-        <v>10</v>
+      <c r="T54" t="n">
+        <v>5</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -45216,18 +44753,13 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
           <t>Reif + Fassung</t>
         </is>
       </c>
+      <c r="X54" t="n">
+        <v>100</v>
+      </c>
       <c r="Y54" t="n">
-        <v>100</v>
-      </c>
-      <c r="Z54" t="n">
         <v>60</v>
       </c>
     </row>
@@ -45306,16 +44838,18 @@
       <c r="R55" t="n">
         <v>0</v>
       </c>
-      <c r="S55" t="n">
-        <v>0</v>
-      </c>
-      <c r="T55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="U55" t="n">
-        <v>14</v>
+      <c r="T55" t="n">
+        <v>7</v>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -45324,18 +44858,13 @@
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
           <t>Reif + Fassung</t>
         </is>
       </c>
+      <c r="X55" t="n">
+        <v>200</v>
+      </c>
       <c r="Y55" t="n">
-        <v>200</v>
-      </c>
-      <c r="Z55" t="n">
         <v>120</v>
       </c>
     </row>
@@ -45414,16 +44943,18 @@
       <c r="R56" t="n">
         <v>0</v>
       </c>
-      <c r="S56" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="U56" t="n">
-        <v>18</v>
+      <c r="T56" t="n">
+        <v>9</v>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -45432,18 +44963,13 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
           <t>Reif + Fassung</t>
         </is>
       </c>
+      <c r="X56" t="n">
+        <v>500</v>
+      </c>
       <c r="Y56" t="n">
-        <v>500</v>
-      </c>
-      <c r="Z56" t="n">
         <v>300</v>
       </c>
     </row>
@@ -45522,16 +45048,18 @@
       <c r="R57" t="n">
         <v>0</v>
       </c>
-      <c r="S57" t="n">
-        <v>0</v>
-      </c>
-      <c r="T57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>INT</t>
         </is>
       </c>
-      <c r="U57" t="n">
-        <v>0</v>
+      <c r="T57" t="n">
+        <v>12</v>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -45540,15 +45068,10 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
           <t>Reif + Fassung</t>
         </is>
       </c>
-      <c r="Z57" t="n">
+      <c r="Y57" t="n">
         <v>1000</v>
       </c>
     </row>

--- a/data/itemliste_v7.xlsx
+++ b/data/itemliste_v7.xlsx
@@ -16717,7 +16717,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Dolche</t>
+          <t>Stichwaffen</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -16766,7 +16766,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Dolche</t>
+          <t>Stichwaffen</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -16815,7 +16815,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Dolche</t>
+          <t>Stichwaffen</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -16864,7 +16864,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Dolche</t>
+          <t>Stichwaffen</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -16913,7 +16913,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Dolche</t>
+          <t>Stichwaffen</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -16962,7 +16962,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Dolche</t>
+          <t>Stichwaffen</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -17011,7 +17011,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Dolche</t>
+          <t>Stichwaffen</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -20176,7 +20176,7 @@
         </is>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
@@ -20283,7 +20283,7 @@
         </is>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P19" t="n">
         <v>2</v>
@@ -20390,7 +20390,7 @@
         </is>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
         <v>3</v>
@@ -20497,7 +20497,7 @@
         </is>
       </c>
       <c r="O21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P21" t="n">
         <v>3</v>
@@ -20604,7 +20604,7 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P22" t="n">
         <v>3</v>
@@ -20711,7 +20711,7 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P23" t="n">
         <v>3</v>
@@ -21699,7 +21699,7 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
         <v>1</v>
@@ -21806,7 +21806,7 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P34" t="n">
         <v>2</v>
@@ -21913,7 +21913,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P35" t="n">
         <v>3</v>
@@ -22020,7 +22020,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P36" t="n">
         <v>3</v>
@@ -22127,7 +22127,7 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P37" t="n">
         <v>3</v>
@@ -22234,7 +22234,7 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P38" t="n">
         <v>3</v>
@@ -23999,7 +23999,7 @@
         </is>
       </c>
       <c r="O56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P56" t="n">
         <v>1</v>
@@ -24106,7 +24106,7 @@
         </is>
       </c>
       <c r="O57" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P57" t="n">
         <v>2</v>
@@ -24213,7 +24213,7 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P58" t="n">
         <v>3</v>
@@ -24320,7 +24320,7 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P59" t="n">
         <v>3</v>
@@ -24427,7 +24427,7 @@
         </is>
       </c>
       <c r="O60" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P60" t="n">
         <v>3</v>
@@ -24534,7 +24534,7 @@
         </is>
       </c>
       <c r="O61" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P61" t="n">
         <v>3</v>
@@ -26268,7 +26268,7 @@
         </is>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P78" t="n">
         <v>1</v>
@@ -26377,7 +26377,7 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P79" t="n">
         <v>2</v>
@@ -26486,7 +26486,7 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P80" t="n">
         <v>3</v>
@@ -26595,7 +26595,7 @@
         </is>
       </c>
       <c r="O81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P81" t="n">
         <v>3</v>
@@ -26704,7 +26704,7 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P82" t="n">
         <v>3</v>
@@ -26813,7 +26813,7 @@
         </is>
       </c>
       <c r="O83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P83" t="n">
         <v>3</v>
@@ -27788,7 +27788,7 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P92" t="n">
         <v>1</v>
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P93" t="n">
         <v>2</v>
@@ -28006,7 +28006,7 @@
         </is>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P94" t="n">
         <v>3</v>
@@ -28115,7 +28115,7 @@
         </is>
       </c>
       <c r="O95" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P95" t="n">
         <v>3</v>
@@ -28224,7 +28224,7 @@
         </is>
       </c>
       <c r="O96" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P96" t="n">
         <v>3</v>
@@ -28333,7 +28333,7 @@
         </is>
       </c>
       <c r="O97" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P97" t="n">
         <v>3</v>
@@ -28548,7 +28548,7 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P99" t="n">
         <v>1</v>
@@ -28657,7 +28657,7 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P100" t="n">
         <v>2</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="O101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P101" t="n">
         <v>3</v>
@@ -28875,7 +28875,7 @@
         </is>
       </c>
       <c r="O102" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P102" t="n">
         <v>3</v>
@@ -28984,7 +28984,7 @@
         </is>
       </c>
       <c r="O103" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P103" t="n">
         <v>3</v>
@@ -29093,7 +29093,7 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="P104" t="n">
         <v>3</v>

--- a/data/itemliste_v7.xlsx
+++ b/data/itemliste_v7.xlsx
@@ -14567,7 +14567,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:J17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14621,6 +14621,16 @@
           <t>Eigenart-Effekt</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Stellar-Eigenart ✦</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Stellar-Effekt</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -14663,6 +14673,16 @@
           <t>+15 % Rohschaden bei Frontalangriff</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Frontmann ✦</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>+25 % Rohschaden bei Frontalangriff</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -14705,6 +14725,16 @@
           <t>Markiert Ziel als 'Opfer' (1 gleichzeitig, springt weiter). Treffer auf Opfer: +20 % Schaden + 20 % Blutungsrisiko</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Erbarmungslos ✦</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Markiert Ziel als 'Opfer' (1 gleichzeitig, springt weiter). Treffer auf Opfer: +30 % Schaden + 30 % Blutungsrisiko</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -14747,6 +14777,16 @@
           <t>Treffen alle Ziele (Ziel + 2 Nachbarn): alle erhalten zusätzlich 30 % des Schadens</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Kollateralschaden ✦</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Treffen alle Ziele (Ziel + 2 Nachbarn): alle erhalten zusätzlich 50 % des Schadens</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -14789,6 +14829,16 @@
           <t>Treffer: Ziel verliert 1 MOB für den nächsten Zug</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Trägheit ✦</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Treffer: Ziel verliert 2 MOB für den nächsten Zug</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -14831,6 +14881,16 @@
           <t>Pusht Ziel 1 Feld zurück. Feld unbegehbar/belegt → 10 % max. LP Schaden + Straucheln (1 Runde, -50 % WID)</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Fliehkraft ✦</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Pusht Ziel 2 Felder zurück. Feld unbegehbar/belegt → 15 % max. LP Schaden + Straucheln (1 Runde, -50 % WID)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -14873,6 +14933,16 @@
           <t>20 % des verursachten Schadens werden als Mana zurückerstattet</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Manavampir ✦</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>35 % des verursachten Schadens werden als Mana zurückerstattet</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -14915,6 +14985,16 @@
           <t>Nach Treffer: sofortige kostenlose Bewegung von 2 Feldern (1x pro Zug, mehrmals pro Runde möglich)</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Duellist ✦</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Nach Treffer: sofortige kostenlose Bewegung von 3 Feldern (1x pro Zug, mehrmals pro Runde möglich)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -14957,6 +15037,16 @@
           <t>Greift zweimal an — je 65 % Schaden pro Stich</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Dopplereffekt ✦</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Greift zweimal an — je 80 % Schaden pro Stich</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -14999,6 +15089,16 @@
           <t>Parieren triggert immer Gegenschlag; universell +20 % Parieren-Chance</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Fechtkunst ✦</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Parieren triggert immer Gegenschlag; universell +35 % Parieren-Chance</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -15041,6 +15141,16 @@
           <t>Backstab triggert immer Blutung; Backstabs haben +50 % Schaden</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Meuchelschlag ✦</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Backstab triggert immer Blutung; Backstabs haben +80 % Schaden</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -15070,7 +15180,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -15081,6 +15191,16 @@
       <c r="H12" t="inlineStr">
         <is>
           <t>Deckt unsichtbare Gegner innerhalb der Bewegungsreichweite (MOB) auf</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Jagdinstinkt ✦</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Deckt unsichtbare Gegner innerhalb der Bewegungsreichweite (MOB) + 2 Felder auf</t>
         </is>
       </c>
     </row>
@@ -15125,6 +15245,16 @@
           <t>Kein Angriff letzten Zug → zweiter Bolzen geladen → nächster Angriff +50 % Schaden</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Techniker ✦</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Kein Angriff letzten Zug → zweiter Bolzen geladen → nächster Angriff +75 % Schaden</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -15154,7 +15284,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -15165,6 +15295,16 @@
       <c r="H14" t="inlineStr">
         <is>
           <t>Keine Bewegung letzten Zug → +30 % Schaden diesen Zug</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Heckenschütze ✦</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Keine Bewegung letzten Zug → +50 % Schaden diesen Zug</t>
         </is>
       </c>
     </row>
@@ -15209,6 +15349,16 @@
           <t>50 % Rüstungsdurchdringung (RD)</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Durchschlagskraft ✦</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>75 % Rüstungsdurchdringung (RD)</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -15251,6 +15401,16 @@
           <t>2 Züge ohne Schadenstreffer → Energieschild (Schutz) in Höhe des max. Mana</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Energiefaser ✦</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Bereits 1 Zug ohne Schadenstreffer → Energieschild (Schutz) in Höhe des max. Mana</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -15291,6 +15451,16 @@
       <c r="H17" t="inlineStr">
         <is>
           <t>Heilungen wirken zu Beginn des nächsten Zuges nochmals zu 20 %</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Segnung ✦</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Heilungen wirken zu Beginn des nächsten Zuges nochmals zu 35 %</t>
         </is>
       </c>
     </row>
@@ -15686,30 +15856,39 @@
           <t>Stellar</t>
         </is>
       </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
+          <t>Spezial</t>
+        </is>
+      </c>
+      <c r="J8" t="n">
+        <v>9</v>
+      </c>
+      <c r="K8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -16020,30 +16199,39 @@
           <t>Stellar</t>
         </is>
       </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
+          <t>Spezial</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>9</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -16354,30 +16542,39 @@
           <t>Stellar</t>
         </is>
       </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
+          <t>Spezial</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>9</v>
+      </c>
+      <c r="K22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -16688,30 +16885,39 @@
           <t>Stellar</t>
         </is>
       </c>
+      <c r="D29" t="n">
+        <v>5</v>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
+          <t>Spezial</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>9</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="30">
@@ -17022,30 +17228,39 @@
           <t>Stellar</t>
         </is>
       </c>
+      <c r="D36" t="n">
+        <v>5</v>
+      </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
+          <t>Spezial</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>11</v>
+      </c>
+      <c r="K36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -17356,30 +17571,39 @@
           <t>Stellar</t>
         </is>
       </c>
+      <c r="D43" t="n">
+        <v>5</v>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
+          <t>Spezial</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>11</v>
+      </c>
+      <c r="K43" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="44">
@@ -17690,30 +17914,39 @@
           <t>Stellar</t>
         </is>
       </c>
+      <c r="D50" t="n">
+        <v>5</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>?</t>
-        </is>
+          <t>Spezial</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>12</v>
+      </c>
+      <c r="K50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -17759,7 +17992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q9"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -17897,10 +18130,8 @@
       <c r="H2" t="n">
         <v>62</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I2" t="n">
+        <v>84</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -17925,10 +18156,8 @@
       <c r="P2" t="n">
         <v>38</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q2" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="3">
@@ -17960,10 +18189,8 @@
       <c r="H3" t="n">
         <v>74</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I3" t="n">
+        <v>100</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -17988,10 +18215,8 @@
       <c r="P3" t="n">
         <v>28</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q3" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="4">
@@ -18023,14 +18248,12 @@
       <c r="H4" t="n">
         <v>62</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I4" t="n">
+        <v>84</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>VIT/INT (typabh.)</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -18051,10 +18274,8 @@
       <c r="P4" t="n">
         <v>40</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q4" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -18086,10 +18307,8 @@
       <c r="H5" t="n">
         <v>52</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I5" t="n">
+        <v>70</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -18114,16 +18333,14 @@
       <c r="P5" t="n">
         <v>40</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q5" t="n">
+        <v>54</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Dolche</t>
+          <t>Stichwaffen</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -18149,10 +18366,8 @@
       <c r="H6" t="n">
         <v>52</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I6" t="n">
+        <v>70</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -18177,10 +18392,8 @@
       <c r="P6" t="n">
         <v>52</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q6" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="7">
@@ -18212,14 +18425,12 @@
       <c r="H7" t="n">
         <v>62</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I7" t="n">
+        <v>84</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -18240,10 +18451,8 @@
       <c r="P7" t="n">
         <v>28</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q7" t="n">
+        <v>38</v>
       </c>
     </row>
     <row r="8">
@@ -18275,10 +18484,8 @@
       <c r="H8" t="n">
         <v>62</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="I8" t="n">
+        <v>84</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -18303,10 +18510,8 @@
       <c r="P8" t="n">
         <v>52</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+      <c r="Q8" t="n">
+        <v>70</v>
       </c>
     </row>
     <row r="9">
@@ -18384,6 +18589,79 @@
         <is>
           <t>—</t>
         </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Kriegsgeräte — Sek-WID (nur Hammer, eingedampft 2026-07-04 = Körper-Rüstungs-Tier)</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>3</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" t="n">
+        <v>7</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="O10" t="n">
+        <v>13</v>
+      </c>
+      <c r="P10" t="n">
+        <v>17</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -19258,7 +19536,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Frontmann</t>
+          <t>Frontmann ✦</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -19267,38 +19545,38 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -19306,7 +19584,7 @@
         </is>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -19314,7 +19592,7 @@
         </is>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="U9" t="n">
         <v>1</v>
@@ -19328,7 +19606,7 @@
         </is>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -20004,7 +20282,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Erbarmungslos</t>
+          <t>Erbarmungslos ✦</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -20013,38 +20291,38 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
@@ -20052,7 +20330,7 @@
         </is>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S16" t="inlineStr">
         <is>
@@ -20060,7 +20338,7 @@
         </is>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>52</v>
       </c>
       <c r="U16" t="n">
         <v>1</v>
@@ -20074,7 +20352,7 @@
         </is>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="17">
@@ -20781,7 +21059,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kollateralschaden</t>
+          <t>Kollateralschaden ✦</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -20790,38 +21068,38 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
@@ -20829,7 +21107,7 @@
         </is>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -20837,7 +21115,7 @@
         </is>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U24" t="n">
         <v>1</v>
@@ -20851,7 +21129,7 @@
         </is>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="25">
@@ -20972,7 +21250,7 @@
         </is>
       </c>
       <c r="T26" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
@@ -21079,7 +21357,7 @@
         </is>
       </c>
       <c r="T27" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U27" t="n">
         <v>1</v>
@@ -21186,7 +21464,7 @@
         </is>
       </c>
       <c r="T28" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
@@ -21293,7 +21571,7 @@
         </is>
       </c>
       <c r="T29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
@@ -21400,7 +21678,7 @@
         </is>
       </c>
       <c r="T30" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
@@ -21507,7 +21785,7 @@
         </is>
       </c>
       <c r="T31" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
@@ -21558,7 +21836,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Trägheit</t>
+          <t>Trägheit ✦</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -21567,38 +21845,38 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
@@ -21606,7 +21884,7 @@
         </is>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S32" t="inlineStr">
         <is>
@@ -21614,7 +21892,7 @@
         </is>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>
@@ -21628,7 +21906,7 @@
         </is>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="33">
@@ -22304,7 +22582,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fliehkraft</t>
+          <t>Fliehkraft ✦</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -22313,38 +22591,38 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
@@ -22352,7 +22630,7 @@
         </is>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
@@ -22360,7 +22638,7 @@
         </is>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="U39" t="n">
         <v>1</v>
@@ -22374,7 +22652,7 @@
         </is>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="40">
@@ -22445,7 +22723,7 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P40" t="n">
         <v>1</v>
@@ -22552,7 +22830,7 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P41" t="n">
         <v>2</v>
@@ -22659,7 +22937,7 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P42" t="n">
         <v>3</v>
@@ -22766,7 +23044,7 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P43" t="n">
         <v>3</v>
@@ -22873,7 +23151,7 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="P44" t="n">
         <v>3</v>
@@ -22980,7 +23258,7 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P45" t="n">
         <v>3</v>
@@ -23050,7 +23328,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Manavampir</t>
+          <t>Manavampir ✦</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -23059,38 +23337,38 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
@@ -23098,7 +23376,7 @@
         </is>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -23106,7 +23384,7 @@
         </is>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="U46" t="n">
         <v>1</v>
@@ -23120,7 +23398,7 @@
         </is>
       </c>
       <c r="Y46" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="47">
@@ -23827,7 +24105,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Duellist</t>
+          <t>Duellist ✦</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -23836,38 +24114,38 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
@@ -23875,7 +24153,7 @@
         </is>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S54" t="inlineStr">
         <is>
@@ -23883,7 +24161,7 @@
         </is>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="U54" t="n">
         <v>1</v>
@@ -23897,7 +24175,7 @@
         </is>
       </c>
       <c r="Y54" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="55">
@@ -24604,7 +24882,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dopplereffekt</t>
+          <t>Dopplereffekt ✦</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -24613,38 +24891,38 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
@@ -24652,7 +24930,7 @@
         </is>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S62" t="inlineStr">
         <is>
@@ -24660,7 +24938,7 @@
         </is>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U62" t="n">
         <v>2</v>
@@ -24674,7 +24952,7 @@
         </is>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="63">
@@ -25350,7 +25628,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Fechtkunst</t>
+          <t>Fechtkunst ✦</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -25359,38 +25637,38 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
@@ -25398,7 +25676,7 @@
         </is>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S69" t="inlineStr">
         <is>
@@ -25406,7 +25684,7 @@
         </is>
       </c>
       <c r="T69" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U69" t="n">
         <v>1</v>
@@ -25420,7 +25698,7 @@
         </is>
       </c>
       <c r="Y69" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="70">
@@ -26096,7 +26374,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Meuchelschlag</t>
+          <t>Meuchelschlag ✦</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -26105,38 +26383,38 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q76" t="inlineStr">
         <is>
@@ -26144,7 +26422,7 @@
         </is>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="S76" t="inlineStr">
         <is>
@@ -26152,7 +26430,7 @@
         </is>
       </c>
       <c r="T76" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U76" t="n">
         <v>1</v>
@@ -26166,7 +26444,7 @@
         </is>
       </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="77">
@@ -26283,7 +26561,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -26392,7 +26670,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -26501,7 +26779,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T80" t="n">
@@ -26610,7 +26888,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T81" t="n">
@@ -26719,7 +26997,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T82" t="n">
@@ -26828,7 +27106,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -26885,7 +27163,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Jagdinstinkt</t>
+          <t>Jagdinstinkt ✦</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -26894,38 +27172,38 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q84" t="inlineStr">
         <is>
@@ -26933,15 +27211,15 @@
         </is>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U84" t="n">
         <v>1</v>
@@ -26957,7 +27235,7 @@
         </is>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="85">
@@ -27645,7 +27923,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Techniker</t>
+          <t>Techniker ✦</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -27654,38 +27932,38 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q91" t="inlineStr">
         <is>
@@ -27693,7 +27971,7 @@
         </is>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -27701,7 +27979,7 @@
         </is>
       </c>
       <c r="T91" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U91" t="n">
         <v>1</v>
@@ -27717,7 +27995,7 @@
         </is>
       </c>
       <c r="Y91" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="92">
@@ -27803,7 +28081,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -27912,7 +28190,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -28021,7 +28299,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -28130,7 +28408,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T95" t="n">
@@ -28239,7 +28517,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T96" t="n">
@@ -28348,7 +28626,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T97" t="n">
@@ -28405,7 +28683,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Heckenschütze</t>
+          <t>Heckenschütze ✦</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -28414,38 +28692,38 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q98" t="inlineStr">
         <is>
@@ -28453,15 +28731,15 @@
         </is>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>WID</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U98" t="n">
         <v>1</v>
@@ -28477,7 +28755,7 @@
         </is>
       </c>
       <c r="Y98" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="99">
@@ -29165,7 +29443,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Durchschlagskraft</t>
+          <t>Durchschlagskraft ✦</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -29174,38 +29452,38 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q105" t="inlineStr">
         <is>
@@ -29213,7 +29491,7 @@
         </is>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S105" t="inlineStr">
         <is>
@@ -29221,7 +29499,7 @@
         </is>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="U105" t="n">
         <v>1</v>
@@ -29237,7 +29515,7 @@
         </is>
       </c>
       <c r="Y105" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="106">
@@ -29944,7 +30222,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Energiefaser</t>
+          <t>Energiefaser ✦</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -29953,38 +30231,38 @@
         </is>
       </c>
       <c r="I113" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q113" t="inlineStr">
         <is>
@@ -29992,7 +30270,7 @@
         </is>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S113" t="inlineStr">
         <is>
@@ -30000,7 +30278,7 @@
         </is>
       </c>
       <c r="T113" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U113" t="n">
         <v>1</v>
@@ -30014,7 +30292,7 @@
         </is>
       </c>
       <c r="Y113" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="114">
@@ -30690,7 +30968,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Segnung</t>
+          <t>Segnung ✦</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -30699,38 +30977,38 @@
         </is>
       </c>
       <c r="I120" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Aktiv</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Passiv</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Reaktiv</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Mod.</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Spezial</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="P120" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q120" t="inlineStr">
         <is>
@@ -30738,7 +31016,7 @@
         </is>
       </c>
       <c r="R120" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="S120" t="inlineStr">
         <is>
@@ -30746,7 +31024,7 @@
         </is>
       </c>
       <c r="T120" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="U120" t="n">
         <v>1</v>
@@ -30760,7 +31038,7 @@
         </is>
       </c>
       <c r="Y120" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
     </row>
   </sheetData>

--- a/data/itemliste_v7.xlsx
+++ b/data/itemliste_v7.xlsx
@@ -662,7 +662,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diamant Robe</t>
+          <t>Kosmium Robe</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Diamant Lederkluft</t>
+          <t>Kosmium Lederkluft</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Diamant Kettenhemd</t>
+          <t>Kosmium Kettenhemd</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3737,7 +3737,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Diamant Schuppenpanzer</t>
+          <t>Kosmium Schuppenpanzer</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4500,7 +4500,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Diamant Plattenpanzer</t>
+          <t>Kosmium Plattenpanzer</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>diamantbearbeiteter Köcher</t>
+          <t>kosmiumbearbeiteter Köcher</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>diamantbeschlagene Buchrolle</t>
+          <t>kosmiumbeschlagene Buchrolle</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6044,7 +6044,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -6980,7 +6980,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>diamantbearbeitete Sandale</t>
+          <t>kosmiumbearbeitete Sandale</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -6998,7 +6998,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -7765,7 +7765,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>diamantbearbeiteter Lederstiefel</t>
+          <t>kosmiumbearbeiteter Lederstiefel</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8550,7 +8550,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Diamant Kettenstiefel</t>
+          <t>Kosmium Kettenstiefel</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -8568,7 +8568,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9335,7 +9335,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Diamant Schuppenstiefel</t>
+          <t>Kosmium Schuppenstiefel</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Diamant Plattenstiefel</t>
+          <t>Kosmium Plattenstiefel</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -10905,7 +10905,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Diamant Steigeisen</t>
+          <t>Kosmium Steigeisen</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -11690,7 +11690,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>diamantbearbeitete Windsohle</t>
+          <t>kosmiumbearbeitete Windsohle</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -11708,7 +11708,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -15804,7 +15804,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -16147,7 +16147,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -16490,7 +16490,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -16833,7 +16833,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -17176,7 +17176,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -17862,7 +17862,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DiamantBreitschwert</t>
+          <t>KosmiumBreitschwert</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -19424,7 +19424,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20152,7 +20152,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DiamantFalchion</t>
+          <t>KosmiumFalchion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -20929,7 +20929,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>DiamantKampfaxt</t>
+          <t>KosmiumKampfaxt</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -20947,7 +20947,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -21706,7 +21706,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DiamantHammer</t>
+          <t>KosmiumHammer</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -21724,7 +21724,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -22452,7 +22452,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DiamantRammbock</t>
+          <t>KosmiumRammbock</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -22470,7 +22470,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -23198,7 +23198,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DiamantZepter</t>
+          <t>KosmiumZepter</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -23216,7 +23216,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -23975,7 +23975,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DiamantPike</t>
+          <t>KosmiumPike</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -23993,7 +23993,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -24752,7 +24752,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DiamantDolchpaar</t>
+          <t>KosmiumDolchpaar</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -25498,7 +25498,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>DiamantRapier</t>
+          <t>KosmiumRapier</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -25516,7 +25516,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -26244,7 +26244,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>DiamantStilett</t>
+          <t>KosmiumStilett</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -26262,7 +26262,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -27031,7 +27031,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>DiamantJagdbogen</t>
+          <t>KosmiumJagdbogen</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -27049,7 +27049,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -27791,7 +27791,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>DiamantRepetierarmbrust</t>
+          <t>KosmiumRepetierarmbrust</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -27809,7 +27809,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -28551,7 +28551,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>DiamantLangbogen</t>
+          <t>KosmiumLangbogen</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -28569,7 +28569,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -29311,7 +29311,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DiamantKriegsarmbrust</t>
+          <t>KosmiumKriegsarmbrust</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -29329,7 +29329,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -30092,7 +30092,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>DiamantZauberstab</t>
+          <t>KosmiumZauberstab</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -30110,7 +30110,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -30838,7 +30838,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Diamantenergiesphäre</t>
+          <t>Kosmiumenergiesphäre</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -30856,7 +30856,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -31265,7 +31265,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Diamant (Selten)</t>
+          <t>Kosmium (Selten)</t>
         </is>
       </c>
     </row>
@@ -31935,7 +31935,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diamant Buckler</t>
+          <t>Kosmium Buckler</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -31953,7 +31953,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -32637,7 +32637,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Diamant Turmschild</t>
+          <t>Kosmium Turmschild</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -32655,7 +32655,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -33339,7 +33339,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>diamantbeschlagener Foliant</t>
+          <t>kosmiumbeschlagener Foliant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -33357,7 +33357,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -34041,7 +34041,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>diamantbeschlagener Energiekristall</t>
+          <t>kosmiumbeschlagener Energiekristall</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -34059,7 +34059,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -34743,7 +34743,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Diamant Kampfkette</t>
+          <t>Kosmium Kampfkette</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -34761,7 +34761,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -35445,7 +35445,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Diamant Laterne</t>
+          <t>Kosmium Laterne</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -35463,7 +35463,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -36147,7 +36147,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>diamantbeschlagener Fester Gürtel</t>
+          <t>kosmiumbeschlagener Fester Gürtel</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -36165,7 +36165,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -36849,7 +36849,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>diamantbearbeitete Fackel</t>
+          <t>kosmiumbearbeitete Fackel</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -36867,7 +36867,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -37551,7 +37551,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>diamantbeschlagenes Signalhorn</t>
+          <t>kosmiumbeschlagenes Signalhorn</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -37569,7 +37569,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -38253,7 +38253,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>diamantbearbeitete Standarte</t>
+          <t>kosmiumbearbeitete Standarte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -38271,7 +38271,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -38955,7 +38955,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Diamant Rauchschwenker</t>
+          <t>Kosmium Rauchschwenker</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -38973,7 +38973,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -39657,7 +39657,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>diamantbearbeiteter Köderkolben</t>
+          <t>kosmiumbearbeiteter Köderkolben</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -39675,7 +39675,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -40576,7 +40576,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>diamantbearbeitete Kapuze</t>
+          <t>kosmiumbearbeitete Kapuze</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -40594,7 +40594,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -41339,7 +41339,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>diamantbearbeitete Lederkappe</t>
+          <t>kosmiumbearbeitete Lederkappe</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -41357,7 +41357,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -42102,7 +42102,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Diamant Kettenhaube</t>
+          <t>Kosmium Kettenhaube</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -42120,7 +42120,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -42865,7 +42865,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Diamant Schuppenhelm</t>
+          <t>Kosmium Schuppenhelm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -42883,7 +42883,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -43628,7 +43628,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Diamant Plattenhelm</t>
+          <t>Kosmium Plattenhelm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -43646,7 +43646,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -44391,7 +44391,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>diamantbeschlagenes Zielvisier</t>
+          <t>kosmiumbeschlagenes Zielvisier</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -44409,7 +44409,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -45154,7 +45154,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Diamant Diadem</t>
+          <t>Kosmium Diadem</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -45172,7 +45172,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Diamant</t>
+          <t>Kosmium</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">

--- a/data/itemliste_v7.xlsx
+++ b/data/itemliste_v7.xlsx
@@ -14811,12 +14811,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
           <t>STR</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>WID</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -14863,12 +14863,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
           <t>STR</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>VIT</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>WID</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -17992,7 +17992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Q11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -18227,55 +18227,83 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>15</v>
-      </c>
-      <c r="E4" t="n">
-        <v>22</v>
-      </c>
-      <c r="F4" t="n">
-        <v>32</v>
-      </c>
-      <c r="G4" t="n">
-        <v>45</v>
-      </c>
-      <c r="H4" t="n">
-        <v>62</v>
-      </c>
-      <c r="I4" t="n">
-        <v>84</v>
+          <t>WID/WIL (typabh., s. u.)</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>VIT/INT (typabh.)</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>6</v>
-      </c>
-      <c r="L4" t="n">
-        <v>9</v>
-      </c>
-      <c r="M4" t="n">
-        <v>14</v>
-      </c>
-      <c r="N4" t="n">
-        <v>20</v>
-      </c>
-      <c r="O4" t="n">
-        <v>28</v>
-      </c>
-      <c r="P4" t="n">
-        <v>40</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>54</v>
+          <t>STR/WID (typabh., s. u.)</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -18594,73 +18622,118 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Kriegsgeräte — Sek-WID (nur Hammer, eingedampft 2026-07-04 = Körper-Rüstungs-Tier)</t>
+          <t>Kriegsgeräte — Hammer &amp; Rammbock: Prim WID / Sek STR (physische Zäh-Bruiser, 2026-07-07)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>7</v>
+      </c>
+      <c r="F10" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" t="n">
+        <v>13</v>
+      </c>
+      <c r="H10" t="n">
+        <v>17</v>
+      </c>
+      <c r="I10" t="n">
+        <v>23</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>6</v>
+      </c>
+      <c r="L10" t="n">
+        <v>9</v>
+      </c>
+      <c r="M10" t="n">
+        <v>14</v>
+      </c>
+      <c r="N10" t="n">
+        <v>20</v>
+      </c>
+      <c r="O10" t="n">
+        <v>28</v>
+      </c>
+      <c r="P10" t="n">
+        <v>40</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Kriegsgeräte — Zepter: Prim WIL / Sek WID (Magie-Nahkämpfer, unverändert Rohschaden-relevant, 2026-07-07)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>WIL</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="n">
+        <v>15</v>
+      </c>
+      <c r="E11" t="n">
+        <v>22</v>
+      </c>
+      <c r="F11" t="n">
+        <v>32</v>
+      </c>
+      <c r="G11" t="n">
+        <v>45</v>
+      </c>
+      <c r="H11" t="n">
+        <v>62</v>
+      </c>
+      <c r="I11" t="n">
+        <v>84</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>WID</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>3</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K11" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" t="n">
         <v>5</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M11" t="n">
         <v>7</v>
       </c>
-      <c r="N10" t="n">
+      <c r="N11" t="n">
         <v>10</v>
       </c>
-      <c r="O10" t="n">
+      <c r="O11" t="n">
         <v>13</v>
       </c>
-      <c r="P10" t="n">
+      <c r="P11" t="n">
         <v>17</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="Q11" t="n">
         <v>23</v>
       </c>
     </row>
@@ -21238,19 +21311,19 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>3</v>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="R26" t="n">
-        <v>10</v>
-      </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
       <c r="T26" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="U26" t="n">
         <v>1</v>
@@ -21345,19 +21418,19 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R27" t="n">
+        <v>5</v>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="R27" t="n">
-        <v>15</v>
-      </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
       <c r="T27" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="U27" t="n">
         <v>1</v>
@@ -21452,19 +21525,19 @@
       </c>
       <c r="Q28" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R28" t="n">
+        <v>7</v>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="R28" t="n">
-        <v>22</v>
-      </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
       <c r="T28" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="U28" t="n">
         <v>1</v>
@@ -21559,19 +21632,19 @@
       </c>
       <c r="Q29" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R29" t="n">
+        <v>10</v>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="R29" t="n">
-        <v>32</v>
-      </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
       <c r="T29" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="U29" t="n">
         <v>1</v>
@@ -21666,19 +21739,19 @@
       </c>
       <c r="Q30" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R30" t="n">
+        <v>13</v>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="R30" t="n">
-        <v>45</v>
-      </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
       <c r="T30" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="U30" t="n">
         <v>1</v>
@@ -21773,19 +21846,19 @@
       </c>
       <c r="Q31" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R31" t="n">
+        <v>17</v>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="R31" t="n">
-        <v>62</v>
-      </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
       <c r="T31" t="n">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="U31" t="n">
         <v>1</v>
@@ -21880,19 +21953,19 @@
       </c>
       <c r="Q32" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R32" t="n">
+        <v>23</v>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="R32" t="n">
-        <v>84</v>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>WID</t>
-        </is>
-      </c>
       <c r="T32" t="n">
-        <v>23</v>
+        <v>54</v>
       </c>
       <c r="U32" t="n">
         <v>1</v>
@@ -21984,15 +22057,15 @@
       </c>
       <c r="Q33" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>3</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
           <t>STR</t>
-        </is>
-      </c>
-      <c r="R33" t="n">
-        <v>10</v>
-      </c>
-      <c r="S33" t="inlineStr">
-        <is>
-          <t>VIT</t>
         </is>
       </c>
       <c r="T33" t="n">
@@ -22091,15 +22164,15 @@
       </c>
       <c r="Q34" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>5</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
           <t>STR</t>
-        </is>
-      </c>
-      <c r="R34" t="n">
-        <v>15</v>
-      </c>
-      <c r="S34" t="inlineStr">
-        <is>
-          <t>VIT</t>
         </is>
       </c>
       <c r="T34" t="n">
@@ -22198,15 +22271,15 @@
       </c>
       <c r="Q35" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>7</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
           <t>STR</t>
-        </is>
-      </c>
-      <c r="R35" t="n">
-        <v>22</v>
-      </c>
-      <c r="S35" t="inlineStr">
-        <is>
-          <t>VIT</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -22305,15 +22378,15 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>10</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
           <t>STR</t>
-        </is>
-      </c>
-      <c r="R36" t="n">
-        <v>32</v>
-      </c>
-      <c r="S36" t="inlineStr">
-        <is>
-          <t>VIT</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -22412,15 +22485,15 @@
       </c>
       <c r="Q37" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>13</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
           <t>STR</t>
-        </is>
-      </c>
-      <c r="R37" t="n">
-        <v>45</v>
-      </c>
-      <c r="S37" t="inlineStr">
-        <is>
-          <t>VIT</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -22519,15 +22592,15 @@
       </c>
       <c r="Q38" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>17</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
           <t>STR</t>
-        </is>
-      </c>
-      <c r="R38" t="n">
-        <v>62</v>
-      </c>
-      <c r="S38" t="inlineStr">
-        <is>
-          <t>VIT</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -22626,15 +22699,15 @@
       </c>
       <c r="Q39" t="inlineStr">
         <is>
+          <t>WID</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>23</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
           <t>STR</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>84</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>VIT</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -22738,11 +22811,11 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>WID</t>
         </is>
       </c>
       <c r="T40" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="U40" t="n">
         <v>1</v>
@@ -22845,11 +22918,11 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>WID</t>
         </is>
       </c>
       <c r="T41" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="U41" t="n">
         <v>1</v>
@@ -22952,11 +23025,11 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>WID</t>
         </is>
       </c>
       <c r="T42" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="U42" t="n">
         <v>1</v>
@@ -23059,11 +23132,11 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>WID</t>
         </is>
       </c>
       <c r="T43" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="U43" t="n">
         <v>1</v>
@@ -23166,11 +23239,11 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>WID</t>
         </is>
       </c>
       <c r="T44" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="U44" t="n">
         <v>1</v>
@@ -23273,11 +23346,11 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>WID</t>
         </is>
       </c>
       <c r="T45" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="U45" t="n">
         <v>1</v>
@@ -23380,11 +23453,11 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>INT</t>
+          <t>WID</t>
         </is>
       </c>
       <c r="T46" t="n">
-        <v>54</v>
+        <v>23</v>
       </c>
       <c r="U46" t="n">
         <v>1</v>
